--- a/output/yearly_surface_area_iteration_66_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_66_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497656029487</v>
+        <v>10.84497629478754</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907273664838</v>
+        <v>37.78907181149417</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.70904282664445</v>
+        <v>4.885176576332128</v>
       </c>
       <c r="C2" t="n">
-        <v>6.360743375815084</v>
+        <v>7.435757111965342</v>
       </c>
       <c r="D2" t="n">
-        <v>25.18477385704342</v>
+        <v>35.05624702324511</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.1273494641116</v>
+        <v>19.43860454408685</v>
       </c>
       <c r="C3" t="n">
-        <v>27.47911824186822</v>
+        <v>23.69448084199677</v>
       </c>
       <c r="D3" t="n">
-        <v>87.03193398147974</v>
+        <v>59.3908273684108</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.78368101436299</v>
+        <v>36.22059980048183</v>
       </c>
       <c r="C4" t="n">
-        <v>74.49599754595221</v>
+        <v>67.06809441562085</v>
       </c>
       <c r="D4" t="n">
-        <v>102.6633209284975</v>
+        <v>70.84585958156258</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.58268477689965</v>
+        <v>43.54051068334605</v>
       </c>
       <c r="C5" t="n">
-        <v>131.2105806725862</v>
+        <v>102.1508486268806</v>
       </c>
       <c r="D5" t="n">
-        <v>67.61787312999908</v>
+        <v>53.57888095926969</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.97868895460962</v>
+        <v>37.31328499530853</v>
       </c>
       <c r="C6" t="n">
-        <v>135.366318704663</v>
+        <v>123.9348484364131</v>
       </c>
       <c r="D6" t="n">
-        <v>45.12210623488766</v>
+        <v>40.49316580936395</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.91282974296706</v>
+        <v>25.3919226226395</v>
       </c>
       <c r="C7" t="n">
-        <v>95.99823576436586</v>
+        <v>134.7448724078747</v>
       </c>
       <c r="D7" t="n">
-        <v>39.04606969330414</v>
+        <v>37.84833749412304</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.4352173326176</v>
+        <v>13.60211444233956</v>
       </c>
       <c r="C8" t="n">
-        <v>58.83123117699011</v>
+        <v>100.5555086074795</v>
       </c>
       <c r="D8" t="n">
-        <v>36.30012136452581</v>
+        <v>36.04977569994287</v>
       </c>
     </row>
     <row r="9">
@@ -881,7 +881,7 @@
         <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>36.16562192904399</v>
+        <v>53.47187045950676</v>
       </c>
       <c r="D9" t="n">
         <v>34.50155957034565</v>
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>34.59188035913637</v>
       </c>
     </row>
     <row r="11">
@@ -912,7 +912,7 @@
         <v>29.67528785626833</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.694479357049303</v>
+        <v>7.685043487975346</v>
       </c>
       <c r="C21" t="n">
-        <v>94.25737212385395</v>
+        <v>93.18115229170107</v>
       </c>
       <c r="D21" t="n">
-        <v>8.656289276680466</v>
+        <v>8.645673923972264</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.805655012288137</v>
+        <v>5.465389469541994</v>
       </c>
       <c r="C2" t="n">
-        <v>5.8787052530299</v>
+        <v>8.374307917225291</v>
       </c>
       <c r="D2" t="n">
-        <v>22.10306781341269</v>
+        <v>31.67903492063608</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.33213382367169</v>
+        <v>17.9758004647591</v>
       </c>
       <c r="C3" t="n">
-        <v>25.90832191507333</v>
+        <v>26.24211613451724</v>
       </c>
       <c r="D3" t="n">
-        <v>86.47233779005906</v>
+        <v>71.15707360380883</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.5629677073567</v>
+        <v>36.16954891986099</v>
       </c>
       <c r="C4" t="n">
-        <v>71.47123286916779</v>
+        <v>63.04783756673017</v>
       </c>
       <c r="D4" t="n">
-        <v>119.7143150558561</v>
+        <v>82.31954500109505</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.92062697133881</v>
+        <v>48.27744335633691</v>
       </c>
       <c r="C5" t="n">
-        <v>132.756833306775</v>
+        <v>111.4038207394068</v>
       </c>
       <c r="D5" t="n">
-        <v>84.8475453395306</v>
+        <v>64.13266877992289</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.82776185006286</v>
+        <v>47.0944373727195</v>
       </c>
       <c r="C6" t="n">
-        <v>170.0229944122796</v>
+        <v>142.3701068267597</v>
       </c>
       <c r="D6" t="n">
-        <v>54.58124536530568</v>
+        <v>47.21519234034186</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.99752208743954</v>
+        <v>34.49468733641593</v>
       </c>
       <c r="C7" t="n">
-        <v>141.4521727232889</v>
+        <v>155.2260930138717</v>
       </c>
       <c r="D7" t="n">
-        <v>42.33983324105218</v>
+        <v>40.36357511240336</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.61041039233004</v>
+        <v>19.86075605691297</v>
       </c>
       <c r="C8" t="n">
-        <v>91.04237335332795</v>
+        <v>138.1073582949201</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -1192,7 +1192,7 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>53.0281204971872</v>
+        <v>85.86561770883451</v>
       </c>
       <c r="D9" t="n">
         <v>35.61093447614454</v>
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>36.58482819875739</v>
+        <v>47.11898106532567</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1237,7 +1237,7 @@
         <v>30.59224021203486</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.874294797149801</v>
+        <v>7.86496720303333</v>
       </c>
       <c r="C21" t="n">
-        <v>102.3658323629474</v>
+        <v>101.2614527390541</v>
       </c>
       <c r="D21" t="n">
-        <v>9.842868496437251</v>
+        <v>9.831209003791662</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.660176425610362</v>
+        <v>6.439283192154829</v>
       </c>
       <c r="C2" t="n">
-        <v>16.67792999974482</v>
+        <v>13.26930197059989</v>
       </c>
       <c r="D2" t="n">
-        <v>28.80251414719292</v>
+        <v>32.008902149263</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.3433339590459</v>
+        <v>17.79908587799467</v>
       </c>
       <c r="C3" t="n">
-        <v>24.24425955637498</v>
+        <v>29.01064466049325</v>
       </c>
       <c r="D3" t="n">
-        <v>84.7051919224148</v>
+        <v>78.33855806037424</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.54645792283375</v>
+        <v>34.53592073999429</v>
       </c>
       <c r="C4" t="n">
-        <v>68.16568834896879</v>
+        <v>64.01780429852602</v>
       </c>
       <c r="D4" t="n">
-        <v>130.052118381575</v>
+        <v>93.80599314078273</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.48513190128072</v>
+        <v>50.46183199828607</v>
       </c>
       <c r="C5" t="n">
-        <v>130.6951631278567</v>
+        <v>112.1646752101981</v>
       </c>
       <c r="D5" t="n">
-        <v>102.3717418603362</v>
+        <v>75.12824306748718</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.3422387048172</v>
+        <v>55.02401357992099</v>
       </c>
       <c r="C6" t="n">
-        <v>188.1764912115074</v>
+        <v>157.7059877147991</v>
       </c>
       <c r="D6" t="n">
-        <v>66.01271563355554</v>
+        <v>54.90325861229863</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.42346172236242</v>
+        <v>43.35790561035613</v>
       </c>
       <c r="C7" t="n">
-        <v>184.810078333645</v>
+        <v>176.3660663294182</v>
       </c>
       <c r="D7" t="n">
-        <v>46.77144237802229</v>
+        <v>43.59745205019235</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.28629478120835</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="C8" t="n">
-        <v>131.6818195706247</v>
+        <v>167.3143524962627</v>
       </c>
       <c r="D8" t="n">
-        <v>40.88979188187965</v>
+        <v>40.13875488813084</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.08906130364597</v>
+        <v>14.19999879422586</v>
       </c>
       <c r="C9" t="n">
-        <v>78.98749329288135</v>
+        <v>123.1406145436774</v>
       </c>
       <c r="D9" t="n">
-        <v>36.83124687252333</v>
+        <v>36.72030938194344</v>
       </c>
     </row>
     <row r="10">
@@ -1517,10 +1517,10 @@
         <v>7.687084524252525</v>
       </c>
       <c r="C10" t="n">
-        <v>47.54604131667303</v>
+        <v>69.46846755250431</v>
       </c>
       <c r="D10" t="n">
-        <v>36.72718161587318</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
+        <v>42.11403126907541</v>
+      </c>
+      <c r="D11" t="n">
         <v>36.60544490054656</v>
-      </c>
-      <c r="D11" t="n">
-        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.06370009425158</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>36.01639627799849</v>
       </c>
     </row>
     <row r="13">
@@ -1573,10 +1573,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>31.65056423721292</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.038878883028131</v>
+        <v>8.029489328835352</v>
       </c>
       <c r="C21" t="n">
-        <v>110.5345846416368</v>
+        <v>109.4017921053817</v>
       </c>
       <c r="D21" t="n">
-        <v>11.05345846416368</v>
+        <v>11.04054782714861</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.970007789524853</v>
+        <v>5.947427592327178</v>
       </c>
       <c r="C2" t="n">
-        <v>11.34016773175491</v>
+        <v>9.022261402028187</v>
       </c>
       <c r="D2" t="n">
-        <v>23.854505717789</v>
+        <v>26.20873671257285</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.74018101573986</v>
+        <v>22.53601855098553</v>
       </c>
       <c r="C3" t="n">
-        <v>44.10010687476672</v>
+        <v>45.97524498987813</v>
       </c>
       <c r="D3" t="n">
-        <v>92.61316968012285</v>
+        <v>83.27674901273569</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.40758952817845</v>
+        <v>24.23640557474101</v>
       </c>
       <c r="C4" t="n">
-        <v>102.5356937269454</v>
+        <v>91.01095742679206</v>
       </c>
       <c r="D4" t="n">
-        <v>121.6925366799134</v>
+        <v>88.22868443295661</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.21895510024282</v>
+        <v>30.99868376159304</v>
       </c>
       <c r="C5" t="n">
-        <v>112.434655828866</v>
+        <v>94.22323591508764</v>
       </c>
       <c r="D5" t="n">
-        <v>66.95519342963247</v>
+        <v>52.98983233672161</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.07678160957628</v>
+        <v>26.88810612391165</v>
       </c>
       <c r="C6" t="n">
-        <v>121.7210073633366</v>
+        <v>116.1662788527081</v>
       </c>
       <c r="D6" t="n">
-        <v>30.79251674370121</v>
+        <v>28.69943063824701</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.42700349808513</v>
+        <v>17.96598298771663</v>
       </c>
       <c r="C7" t="n">
-        <v>92.58469899669969</v>
+        <v>117.6173019595849</v>
       </c>
       <c r="D7" t="n">
-        <v>28.7455727803466</v>
+        <v>28.20659329071511</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.763480918734528</v>
+        <v>9.846929473595507</v>
       </c>
       <c r="C8" t="n">
-        <v>58.16364273810228</v>
+        <v>90.70857913388404</v>
       </c>
       <c r="D8" t="n">
-        <v>27.12078032981814</v>
+        <v>27.03733177495716</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>5.435937038414587</v>
       </c>
       <c r="C9" t="n">
-        <v>36.27655941962388</v>
+        <v>53.0281204971872</v>
       </c>
       <c r="D9" t="n">
-        <v>27.95624762613216</v>
+        <v>27.62343515439249</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
+        <v>33.02599277086271</v>
+      </c>
+      <c r="D10" t="n">
         <v>28.61303684027329</v>
-      </c>
-      <c r="D10" t="n">
-        <v>28.47068342315751</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>28.78680618392497</v>
       </c>
     </row>
     <row r="12">
@@ -1870,10 +1870,10 @@
         <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
         <v>7.397468951499714</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.518583772020568</v>
+        <v>3.723769042208152</v>
       </c>
       <c r="C2" t="n">
-        <v>4.779147824273473</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="D2" t="n">
-        <v>16.36769772520282</v>
+        <v>19.01252604044373</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.52696183746906</v>
+        <v>22.18749811597792</v>
       </c>
       <c r="C3" t="n">
-        <v>45.14566817978957</v>
+        <v>41.35612204139689</v>
       </c>
       <c r="D3" t="n">
-        <v>90.90001993621217</v>
+        <v>84.97517254108267</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.39330528097125</v>
+        <v>32.45559735469531</v>
       </c>
       <c r="C4" t="n">
-        <v>108.9425792448601</v>
+        <v>104.8712715153485</v>
       </c>
       <c r="D4" t="n">
-        <v>138.6159036057199</v>
+        <v>106.9388321804923</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.23782929080177</v>
+        <v>34.82749980815561</v>
       </c>
       <c r="C5" t="n">
-        <v>150.4773793684299</v>
+        <v>130.1306581979147</v>
       </c>
       <c r="D5" t="n">
-        <v>87.03193398147975</v>
+        <v>66.95519342963247</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.7057220351</v>
+        <v>32.16107304342126</v>
       </c>
       <c r="C6" t="n">
-        <v>150.7827029044506</v>
+        <v>136.4933650691383</v>
       </c>
       <c r="D6" t="n">
-        <v>38.88309957439917</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.5287043486993</v>
+        <v>16.94791061841269</v>
       </c>
       <c r="C7" t="n">
-        <v>123.186756685777</v>
+        <v>141.3922861133299</v>
       </c>
       <c r="D7" t="n">
-        <v>31.32069700858599</v>
+        <v>30.60205768907732</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>8.344855486097888</v>
       </c>
       <c r="C8" t="n">
-        <v>78.85888434362504</v>
+        <v>116.5776311407875</v>
       </c>
       <c r="D8" t="n">
-        <v>28.37250865273282</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>4.548437113775471</v>
       </c>
       <c r="C9" t="n">
-        <v>41.04687151455913</v>
+        <v>58.3531200450219</v>
       </c>
       <c r="D9" t="n">
-        <v>28.84374755077128</v>
+        <v>28.6218725696115</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>35.01894061048373</v>
       </c>
       <c r="D10" t="n">
         <v>29.89421759431538</v>
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
+        <v>29.67528785626833</v>
+      </c>
+      <c r="D11" t="n">
         <v>29.49759152179966</v>
-      </c>
-      <c r="D11" t="n">
-        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2167,7 +2167,7 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
         <v>28.42257778564941</v>
@@ -2181,7 +2181,7 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
         <v>25.23582473766426</v>
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
         <v>6.018113427032947</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.922082078466007</v>
+        <v>4.449280595646544</v>
       </c>
       <c r="C2" t="n">
-        <v>5.687264450701772</v>
+        <v>5.580253950938871</v>
       </c>
       <c r="D2" t="n">
-        <v>25.39486786575225</v>
+        <v>20.84839424738527</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.72268948351267</v>
+        <v>17.55364895193297</v>
       </c>
       <c r="C3" t="n">
-        <v>31.17539834835747</v>
+        <v>28.42159603794516</v>
       </c>
       <c r="D3" t="n">
-        <v>83.55654710844604</v>
+        <v>81.39670215910306</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.44734246243383</v>
+        <v>37.01188845010475</v>
       </c>
       <c r="C4" t="n">
-        <v>110.8059363875205</v>
+        <v>103.9778811044839</v>
       </c>
       <c r="D4" t="n">
-        <v>150.3448434283565</v>
+        <v>122.279621807053</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.72932503773092</v>
+        <v>41.33157834879072</v>
       </c>
       <c r="C5" t="n">
-        <v>176.5427809161827</v>
+        <v>161.0557108816893</v>
       </c>
       <c r="D5" t="n">
-        <v>111.9437819767426</v>
+        <v>86.22199212547613</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.13969557810609</v>
+        <v>39.20511282139213</v>
       </c>
       <c r="C6" t="n">
-        <v>191.7186369284299</v>
+        <v>171.1902924326291</v>
       </c>
       <c r="D6" t="n">
-        <v>53.29319237733387</v>
+        <v>45.12210623488766</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.89475737366311</v>
+        <v>25.21226279276233</v>
       </c>
       <c r="C7" t="n">
-        <v>167.9220543251914</v>
+        <v>169.2994463542497</v>
       </c>
       <c r="D7" t="n">
-        <v>34.61446055633404</v>
+        <v>33.17718191731671</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.93314334511998</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="C8" t="n">
-        <v>116.8279768053704</v>
+        <v>149.957053085179</v>
       </c>
       <c r="D8" t="n">
-        <v>29.95803119509142</v>
+        <v>29.70768553050848</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>65.12030697039516</v>
+        <v>94.85155444580556</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>39.43189654107314</v>
+        <v>49.25428232206248</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.60598467989432</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>34.47308888692249</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2492,7 +2492,7 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.47158305540374</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
+        <v>14.46605242207675</v>
+      </c>
+      <c r="D16" t="n">
         <v>14.87936820556466</v>
-      </c>
-      <c r="D16" t="n">
-        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>33.70830742531424</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>34.9050578767911</v>
       </c>
       <c r="D19" t="n">
         <v>4.212679398923063</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.333614292994668</v>
+        <v>2.634029090494193</v>
       </c>
       <c r="C2" t="n">
-        <v>2.68704346652352</v>
+        <v>2.611448893296516</v>
       </c>
       <c r="D2" t="n">
-        <v>17.73232703410589</v>
+        <v>14.55048272464198</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.04666622591412</v>
+        <v>18.0199791114502</v>
       </c>
       <c r="C3" t="n">
-        <v>29.30516897176729</v>
+        <v>27.38094347144354</v>
       </c>
       <c r="D3" t="n">
-        <v>86.19744843286996</v>
+        <v>81.94648087348126</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.81670058340888</v>
+        <v>40.94280625790898</v>
       </c>
       <c r="C4" t="n">
-        <v>110.4868683836403</v>
+        <v>101.9741340401162</v>
       </c>
       <c r="D4" t="n">
-        <v>159.3297984176234</v>
+        <v>132.5791369723063</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.42283982755667</v>
+        <v>42.90237467558562</v>
       </c>
       <c r="C5" t="n">
-        <v>210.8303194870026</v>
+        <v>195.2450746820845</v>
       </c>
       <c r="D5" t="n">
-        <v>118.202423591316</v>
+        <v>91.67069188404594</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.10194719698821</v>
+        <v>31.55729820530948</v>
       </c>
       <c r="C6" t="n">
-        <v>226.9790874741583</v>
+        <v>206.0482264196164</v>
       </c>
       <c r="D6" t="n">
-        <v>52.16614601285853</v>
+        <v>44.80009298789471</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.905032514595317</v>
+        <v>8.024805734513427</v>
       </c>
       <c r="C7" t="n">
-        <v>166.9039819558875</v>
+        <v>185.5886042631128</v>
       </c>
       <c r="D7" t="n">
-        <v>34.6743471662931</v>
+        <v>33.53650157707104</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>83.44855486097887</v>
+        <v>115.4093513727338</v>
       </c>
       <c r="D8" t="n">
-        <v>31.79389940203295</v>
+        <v>31.37665662772806</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>30.06405994715006</v>
+        <v>37.60780930658255</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.90832191507333</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.48831382410494</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>14.97067074205961</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>12.18348900970292</v>
+      </c>
+      <c r="D15" t="n">
         <v>12.541826921753</v>
-      </c>
-      <c r="D15" t="n">
-        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>29.96293993361265</v>
       </c>
       <c r="D18" t="n">
         <v>3.21031499288707</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.874557278034661</v>
+        <v>3.491094836301658</v>
       </c>
       <c r="C2" t="n">
-        <v>5.175773896789184</v>
+        <v>5.62345084992573</v>
       </c>
       <c r="D2" t="n">
-        <v>18.44507586738908</v>
+        <v>13.34784178693963</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.07058802371454</v>
+        <v>13.6806542586793</v>
       </c>
       <c r="C3" t="n">
-        <v>19.71840263979719</v>
+        <v>18.62375394956199</v>
       </c>
       <c r="D3" t="n">
-        <v>81.563599268825</v>
+        <v>75.97254609313943</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.13202152292136</v>
+        <v>37.89251614081414</v>
       </c>
       <c r="C4" t="n">
-        <v>93.11680625240146</v>
+        <v>85.3698351181899</v>
       </c>
       <c r="D4" t="n">
-        <v>164.4348864797068</v>
+        <v>140.9004305135022</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.17235529425349</v>
+        <v>51.0999680060465</v>
       </c>
       <c r="C5" t="n">
-        <v>209.1858920823892</v>
+        <v>193.4288414292279</v>
       </c>
       <c r="D5" t="n">
-        <v>141.6907374154209</v>
+        <v>112.3855684436536</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.99127174831558</v>
+        <v>42.0629803884546</v>
       </c>
       <c r="C6" t="n">
-        <v>276.1666109523321</v>
+        <v>254.3502134685594</v>
       </c>
       <c r="D6" t="n">
-        <v>70.52090109145691</v>
+        <v>58.36490101747288</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.16938468894497</v>
+        <v>17.54677671800324</v>
       </c>
       <c r="C7" t="n">
-        <v>237.0312022179414</v>
+        <v>237.7498415374501</v>
       </c>
       <c r="D7" t="n">
-        <v>40.12402867256714</v>
+        <v>37.72856427420492</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.17381040138069</v>
+        <v>5.257258956241669</v>
       </c>
       <c r="C8" t="n">
-        <v>137.6066669657542</v>
+        <v>169.4840149226481</v>
       </c>
       <c r="D8" t="n">
-        <v>33.54631905411351</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>56.24530772400399</v>
+        <v>76.10311853780424</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>33.88011327355743</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3089,7 +3089,7 @@
         <v>23.98900515327081</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
         <v>21.47965802121596</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.1456838753228</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.839795197758523</v>
+        <v>2.316924582022473</v>
       </c>
       <c r="C2" t="n">
-        <v>2.713550654538184</v>
+        <v>2.922662915542754</v>
       </c>
       <c r="D2" t="n">
-        <v>14.13422169804133</v>
+        <v>9.868527923088937</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.20665004397734</v>
+        <v>13.04251825091887</v>
       </c>
       <c r="C3" t="n">
-        <v>20.27309009269663</v>
+        <v>20.48907458763093</v>
       </c>
       <c r="D3" t="n">
-        <v>79.18776982454773</v>
+        <v>70.73001335246146</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.76266340194631</v>
+        <v>33.9488356128547</v>
       </c>
       <c r="C4" t="n">
-        <v>76.48698189016474</v>
+        <v>70.33535077535424</v>
       </c>
       <c r="D4" t="n">
-        <v>166.9491423502828</v>
+        <v>145.5715860903086</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.02571503342222</v>
+        <v>55.34602682691395</v>
       </c>
       <c r="C5" t="n">
-        <v>202.1663959970245</v>
+        <v>186.1393647251953</v>
       </c>
       <c r="D5" t="n">
-        <v>157.1532637573082</v>
+        <v>129.3943474197296</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.9082651618111</v>
+        <v>49.79129831628549</v>
       </c>
       <c r="C6" t="n">
-        <v>307.7641608135157</v>
+        <v>284.3779487506524</v>
       </c>
       <c r="D6" t="n">
-        <v>85.69577535599986</v>
+        <v>69.6756163181004</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.49255961009142</v>
+        <v>15.81006502919063</v>
       </c>
       <c r="C7" t="n">
-        <v>294.0432548989622</v>
+        <v>288.4139135628109</v>
       </c>
       <c r="D7" t="n">
-        <v>44.73529763941441</v>
+        <v>42.39971985101125</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>180.0819813899924</v>
+        <v>212.4600206760522</v>
       </c>
       <c r="D8" t="n">
-        <v>34.54770171244525</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -3366,10 +3366,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>64.45468202691582</v>
+        <v>87.52968006753285</v>
       </c>
       <c r="D9" t="n">
         <v>32.50468473990763</v>
@@ -3383,10 +3383,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>34.16482010778901</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
         <v>19.96089432274615</v>
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.695879195861741</v>
+        <v>2.96095107600838</v>
       </c>
       <c r="C2" t="n">
-        <v>3.195588777323368</v>
+        <v>5.618542111404496</v>
       </c>
       <c r="D2" t="n">
-        <v>17.13346093451534</v>
+        <v>16.71818165561893</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.855364292306231</v>
+        <v>10.53906160508951</v>
       </c>
       <c r="C3" t="n">
-        <v>15.86504290062846</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D3" t="n">
-        <v>73.09602531969627</v>
+        <v>63.63197745075702</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.66583023212436</v>
+        <v>29.48188355853172</v>
       </c>
       <c r="C4" t="n">
-        <v>65.07711007140833</v>
+        <v>61.65670106981243</v>
       </c>
       <c r="D4" t="n">
-        <v>167.4724138766464</v>
+        <v>146.6564173035013</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.48575379608648</v>
+        <v>54.19247327442395</v>
       </c>
       <c r="C5" t="n">
-        <v>176.2728002975148</v>
+        <v>161.742934274662</v>
       </c>
       <c r="D5" t="n">
-        <v>174.3829359668397</v>
+        <v>145.6913593102267</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.91205328390785</v>
+        <v>59.08943082320704</v>
       </c>
       <c r="C6" t="n">
-        <v>314.1239224416265</v>
+        <v>289.9729289171549</v>
       </c>
       <c r="D6" t="n">
-        <v>106.0631132283042</v>
+        <v>86.54106012935635</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.64954143177966</v>
+        <v>30.06307819944583</v>
       </c>
       <c r="C7" t="n">
-        <v>353.330998758427</v>
+        <v>338.4192328786222</v>
       </c>
       <c r="D7" t="n">
-        <v>53.95783557310894</v>
+        <v>48.74770050667112</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.510369937488099</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>260.526388275976</v>
+        <v>281.2216298814988</v>
       </c>
       <c r="D8" t="n">
-        <v>37.1346069131356</v>
+        <v>36.88426124855267</v>
       </c>
     </row>
     <row r="9">
@@ -3677,10 +3677,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>119.2578023733813</v>
+        <v>151.3187371509693</v>
       </c>
       <c r="D9" t="n">
         <v>33.39218466454675</v>
@@ -3694,10 +3694,10 @@
         <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>46.6919208139783</v>
+        <v>57.36842709766236</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.8983245115816</v>
+        <v>28.60910984945629</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>24.87748682561417</v>
       </c>
     </row>
     <row r="12">
@@ -3725,7 +3725,7 @@
         <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.313799412460485</v>
+        <v>4.41982816451914</v>
       </c>
       <c r="C2" t="n">
-        <v>5.041274461307371</v>
+        <v>11.56793319914017</v>
       </c>
       <c r="D2" t="n">
-        <v>7.806857744170636</v>
+        <v>6.674902641174064</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.948769192929919</v>
+        <v>2.118611545764617</v>
       </c>
       <c r="C2" t="n">
-        <v>1.840776945462769</v>
+        <v>3.235840433197487</v>
       </c>
       <c r="D2" t="n">
-        <v>12.74701219194058</v>
+        <v>12.30424397732527</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.81533362061036</v>
+        <v>13.95063487734718</v>
       </c>
       <c r="C3" t="n">
-        <v>17.28366833326509</v>
+        <v>20.19455027635689</v>
       </c>
       <c r="D3" t="n">
-        <v>79.29576207201488</v>
+        <v>70.22441328477434</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.4420738710141</v>
+        <v>40.82794177651211</v>
       </c>
       <c r="C4" t="n">
-        <v>95.46514676095984</v>
+        <v>89.49219372832225</v>
       </c>
       <c r="D4" t="n">
-        <v>171.2757044828986</v>
+        <v>149.1068595733013</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.96155727528091</v>
+        <v>34.77841242294326</v>
       </c>
       <c r="C5" t="n">
-        <v>265.4154918431252</v>
+        <v>244.185197738788</v>
       </c>
       <c r="D5" t="n">
-        <v>157.2268948351267</v>
+        <v>130.744250513069</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.54343056426301</v>
+        <v>18.6365166697172</v>
       </c>
       <c r="C6" t="n">
-        <v>291.2207302492527</v>
+        <v>279.7087566692545</v>
       </c>
       <c r="D6" t="n">
-        <v>82.8781594448115</v>
+        <v>70.3196428120863</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.970588626601601</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="C7" t="n">
-        <v>183.1931398647505</v>
+        <v>197.745586084801</v>
       </c>
       <c r="D7" t="n">
-        <v>32.93763547748049</v>
+        <v>32.09922293805371</v>
       </c>
     </row>
     <row r="8">
@@ -4285,10 +4285,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>1.668971097219577</v>
       </c>
       <c r="C8" t="n">
-        <v>87.87132826861075</v>
+        <v>111.4872692942678</v>
       </c>
       <c r="D8" t="n">
         <v>24.53387512912779</v>
@@ -4302,10 +4302,10 @@
         <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>35.61093447614454</v>
+        <v>43.70937128847648</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.78007281871549</v>
+        <v>22.34948648717864</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>19.50241814486289</v>
       </c>
     </row>
     <row r="11">
@@ -4333,7 +4333,7 @@
         <v>15.81497376771187</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="D12" t="n">
-        <v>13.23494080095125</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
         <v>2.5083653843506</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.120215188274616</v>
+        <v>6.238024912784233</v>
       </c>
       <c r="C2" t="n">
-        <v>4.336379609658161</v>
+        <v>7.561420818108934</v>
       </c>
       <c r="D2" t="n">
-        <v>14.30897278939726</v>
+        <v>8.19955682586936</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.169523557665208</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C3" t="n">
-        <v>12.90507357232432</v>
+        <v>29.1480893390878</v>
       </c>
       <c r="D3" t="n">
-        <v>9.694758579437254</v>
+        <v>8.742463306317847</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4557,7 +4557,7 @@
         <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4669,7 +4669,7 @@
         <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>23.93500902953724</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39905696568</v>
+        <v>13.39811134327514</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14800411444233</v>
+        <v>70.14305350302867</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576359643021176</v>
+        <v>1.576248393326487</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.214642894331557</v>
+        <v>4.315762907868979</v>
       </c>
       <c r="C2" t="n">
-        <v>5.631304831559704</v>
+        <v>4.607341976030281</v>
       </c>
       <c r="D2" t="n">
-        <v>20.37911884475529</v>
+        <v>14.39733008277947</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.31173810606075</v>
+        <v>16.64553232550467</v>
       </c>
       <c r="C3" t="n">
-        <v>15.45761760336603</v>
+        <v>29.35916509550086</v>
       </c>
       <c r="D3" t="n">
-        <v>19.36988220478957</v>
+        <v>13.51375714895735</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.78449853115121</v>
+        <v>11.03975293425538</v>
       </c>
       <c r="C4" t="n">
-        <v>20.52245400957532</v>
+        <v>44.95030038664446</v>
       </c>
       <c r="D4" t="n">
-        <v>20.15233512507428</v>
+        <v>19.65458903902115</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>3.043417883165113</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.424156065963628</v>
       </c>
       <c r="D5" t="n">
         <v>29.10881943091793</v>
@@ -4879,10 +4879,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
         <v>34.77743067523902</v>
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
@@ -4924,7 +4924,7 @@
         <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4938,7 +4938,7 @@
         <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>40.5049467818149</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44465364578431</v>
+        <v>15.44115279672366</v>
       </c>
       <c r="C21" t="n">
-        <v>86.16490981332301</v>
+        <v>86.14537876066886</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251506030691434</v>
+        <v>3.250769009836561</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.740458753180348</v>
+        <v>3.986877426946297</v>
       </c>
       <c r="C2" t="n">
-        <v>10.0187353218387</v>
+        <v>5.159084185816988</v>
       </c>
       <c r="D2" t="n">
-        <v>25.09641656366122</v>
+        <v>19.77730750205199</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.34471661737765</v>
+        <v>15.68832831386403</v>
       </c>
       <c r="C3" t="n">
-        <v>19.36988220478957</v>
+        <v>22.42802630351838</v>
       </c>
       <c r="D3" t="n">
-        <v>31.17539834835747</v>
+        <v>21.89297380470387</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.47515019332223</v>
+        <v>23.04947260030661</v>
       </c>
       <c r="C4" t="n">
-        <v>31.02617269731195</v>
+        <v>61.78432827136452</v>
       </c>
       <c r="D4" t="n">
-        <v>25.33399950808894</v>
+        <v>22.02845498788993</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.989282890711298</v>
+        <v>10.01382658331747</v>
       </c>
       <c r="C5" t="n">
-        <v>24.24916829489622</v>
+        <v>49.62734644967627</v>
       </c>
       <c r="D5" t="n">
-        <v>29.69786805346602</v>
+        <v>29.52606220522283</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.11574841810989</v>
       </c>
       <c r="D6" t="n">
         <v>36.6290068454485</v>
@@ -5204,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
@@ -5232,10 +5232,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
         <v>41.26874649571891</v>
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
         <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5361,7 +5361,7 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74271948010638</v>
+        <v>16.73398973412051</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1305888286489</v>
+        <v>102.0773373781351</v>
       </c>
       <c r="D21" t="n">
-        <v>5.022815844031912</v>
+        <v>5.020196920236154</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.906775025825558</v>
+        <v>6.303802008968769</v>
       </c>
       <c r="C2" t="n">
-        <v>10.78449853115121</v>
+        <v>5.834526606338795</v>
       </c>
       <c r="D2" t="n">
-        <v>25.92795686915826</v>
+        <v>24.77342156896401</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.96045235438964</v>
+        <v>14.57895340806514</v>
       </c>
       <c r="C3" t="n">
-        <v>30.83669539039231</v>
+        <v>21.02903582496668</v>
       </c>
       <c r="D3" t="n">
-        <v>43.31470871136928</v>
+        <v>32.05406254365836</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.30396623988479</v>
+        <v>27.13354304997335</v>
       </c>
       <c r="C4" t="n">
-        <v>40.95556897806419</v>
+        <v>58.63193639302801</v>
       </c>
       <c r="D4" t="n">
-        <v>34.47210713921825</v>
+        <v>27.72062817711294</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.08932334555324</v>
+        <v>22.16295442337175</v>
       </c>
       <c r="C5" t="n">
-        <v>42.43604451606839</v>
+        <v>83.96397240570847</v>
       </c>
       <c r="D5" t="n">
-        <v>32.25041208450773</v>
+        <v>30.55689729468198</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.740900721536855</v>
+        <v>9.861655689159212</v>
       </c>
       <c r="C6" t="n">
-        <v>25.96231803880691</v>
+        <v>47.21519234034186</v>
       </c>
       <c r="D6" t="n">
-        <v>38.19882142453915</v>
+        <v>38.15856976866503</v>
       </c>
     </row>
     <row r="7">
@@ -5515,7 +5515,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
         <v>21.19985992550562</v>
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>31.54355373745002</v>
       </c>
       <c r="D8" t="n">
         <v>40.38910055271378</v>
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>42.3781214015178</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5686,7 +5686,7 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.91411459030757</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07460773214065</v>
+        <v>18.05806134647355</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9152980620604</v>
+        <v>117.8073525936608</v>
       </c>
       <c r="D21" t="n">
-        <v>6.885564850339295</v>
+        <v>6.879261465323257</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.680392216772045</v>
+        <v>6.614034283510762</v>
       </c>
       <c r="C2" t="n">
-        <v>8.386088889676254</v>
+        <v>8.561821728736433</v>
       </c>
       <c r="D2" t="n">
-        <v>40.64730019893069</v>
+        <v>22.17179015270996</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.95063487734718</v>
+        <v>16.50317890838888</v>
       </c>
       <c r="C3" t="n">
-        <v>35.08766294978101</v>
+        <v>20.63633674326795</v>
       </c>
       <c r="D3" t="n">
-        <v>50.22130381074558</v>
+        <v>41.1548637620263</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.56524999793468</v>
+        <v>20.06299608398782</v>
       </c>
       <c r="C4" t="n">
-        <v>51.63796574797373</v>
+        <v>46.22657240216531</v>
       </c>
       <c r="D4" t="n">
-        <v>41.32568786256524</v>
+        <v>32.3024447128328</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18.8986433067511</v>
+        <v>19.41406085148068</v>
       </c>
       <c r="C5" t="n">
-        <v>45.0622196249286</v>
+        <v>71.52032025438015</v>
       </c>
       <c r="D5" t="n">
-        <v>30.38509144643879</v>
+        <v>26.92443078896878</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.94845039776043</v>
+        <v>10.82769543013807</v>
       </c>
       <c r="C6" t="n">
-        <v>32.12082138754715</v>
+        <v>62.51082157250717</v>
       </c>
       <c r="D6" t="n">
-        <v>30.67176177607885</v>
+        <v>30.59125846433062</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>5.150248456478767</v>
       </c>
       <c r="C7" t="n">
-        <v>19.10382857693868</v>
+        <v>28.80545939030566</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>30.72183090899544</v>
       </c>
     </row>
     <row r="8">
@@ -5843,7 +5843,7 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D8" t="n">
         <v>30.37527396939631</v>
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.18749811597791</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5874,7 +5874,7 @@
         <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5969,10 +5969,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.066464228173876</v>
+        <v>7.056727853065494</v>
       </c>
       <c r="C21" t="n">
-        <v>66.24810213913008</v>
+        <v>66.15682362248901</v>
       </c>
       <c r="D21" t="n">
-        <v>5.299848171130407</v>
+        <v>5.292545889799121</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.472842540548468</v>
+        <v>5.501714134599125</v>
       </c>
       <c r="C2" t="n">
-        <v>6.42062998577414</v>
+        <v>7.316965639751478</v>
       </c>
       <c r="D2" t="n">
-        <v>35.80335702617693</v>
+        <v>16.3755517068368</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.62728002975148</v>
+        <v>20.62651926622549</v>
       </c>
       <c r="C3" t="n">
-        <v>33.59049770080462</v>
+        <v>28.9026524130261</v>
       </c>
       <c r="D3" t="n">
-        <v>73.85687979048754</v>
+        <v>49.8335134675681</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.54271085846601</v>
+        <v>27.74615361742335</v>
       </c>
       <c r="C4" t="n">
-        <v>74.87887915060848</v>
+        <v>49.74908316500287</v>
       </c>
       <c r="D4" t="n">
-        <v>57.66196966123216</v>
+        <v>46.0606570401476</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.05911015089984</v>
+        <v>25.72178985126644</v>
       </c>
       <c r="C5" t="n">
-        <v>76.40451508300804</v>
+        <v>79.52156404399165</v>
       </c>
       <c r="D5" t="n">
-        <v>39.34353924769093</v>
+        <v>33.1830724035422</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.56230475482195</v>
+        <v>19.8843180018149</v>
       </c>
       <c r="C6" t="n">
-        <v>55.74854338565514</v>
+        <v>93.26308666033425</v>
       </c>
       <c r="D6" t="n">
-        <v>33.61013265488955</v>
+        <v>32.4428346345401</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.761517423326035</v>
+        <v>9.701630813366979</v>
       </c>
       <c r="C7" t="n">
-        <v>35.39298648580176</v>
+        <v>65.27640485537042</v>
       </c>
       <c r="D7" t="n">
-        <v>33.65627479698915</v>
+        <v>33.29695513723482</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>22.94835258676919</v>
+        <v>30.29182541453534</v>
       </c>
       <c r="D8" t="n">
-        <v>32.46148784092078</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.28437234352885</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6224,10 +6224,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.289790204256263</v>
+        <v>7.279171513620195</v>
       </c>
       <c r="C21" t="n">
-        <v>75.63157336915873</v>
+        <v>75.52140445380954</v>
       </c>
       <c r="D21" t="n">
-        <v>6.378566428724231</v>
+        <v>6.36927507441767</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.57356164345839</v>
+        <v>5.659775514982861</v>
       </c>
       <c r="C2" t="n">
-        <v>6.923284810348507</v>
+        <v>5.114905539125882</v>
       </c>
       <c r="D2" t="n">
-        <v>27.5478405811655</v>
+        <v>26.32752818478671</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.42463909204914</v>
+        <v>19.74294633240336</v>
       </c>
       <c r="C3" t="n">
-        <v>28.37250865273282</v>
+        <v>28.6424892714007</v>
       </c>
       <c r="D3" t="n">
-        <v>85.36296288426017</v>
+        <v>51.36994862471436</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.2093586073786</v>
+        <v>34.67631066170159</v>
       </c>
       <c r="C4" t="n">
-        <v>80.36684881734816</v>
+        <v>63.09888844735099</v>
       </c>
       <c r="D4" t="n">
-        <v>81.70693443364505</v>
+        <v>60.68673433801658</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.39138284329177</v>
+        <v>34.63115026730624</v>
       </c>
       <c r="C5" t="n">
-        <v>111.7965198211056</v>
+        <v>85.92746781420209</v>
       </c>
       <c r="D5" t="n">
-        <v>50.80544369477245</v>
+        <v>41.94517066394498</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.57238427377167</v>
+        <v>28.01515248838698</v>
       </c>
       <c r="C6" t="n">
-        <v>91.29075552250242</v>
+        <v>112.1411132652962</v>
       </c>
       <c r="D6" t="n">
-        <v>38.76234460677682</v>
+        <v>35.98498035146259</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.94791061841269</v>
+        <v>17.36711688812607</v>
       </c>
       <c r="C7" t="n">
-        <v>60.48547605864599</v>
+        <v>104.0829281088383</v>
       </c>
       <c r="D7" t="n">
-        <v>35.81219275551515</v>
+        <v>35.2133266559246</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.344855486097888</v>
+        <v>8.261406931236909</v>
       </c>
       <c r="C8" t="n">
-        <v>36.30012136452581</v>
+        <v>61.16779071309751</v>
       </c>
       <c r="D8" t="n">
-        <v>34.63115026730623</v>
+        <v>34.46425315758427</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>26.84687272033327</v>
+        <v>31.28437234352885</v>
       </c>
       <c r="D9" t="n">
         <v>32.8374972116473</v>
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6507,7 +6507,7 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
         <v>35.89465956267188</v>
@@ -6524,7 +6524,7 @@
         <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.499451323586391</v>
+        <v>7.489415296720003</v>
       </c>
       <c r="C21" t="n">
-        <v>85.3062588057952</v>
+        <v>84.25592208810005</v>
       </c>
       <c r="D21" t="n">
-        <v>7.499451323586391</v>
+        <v>7.489415296720003</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_66_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_66_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497629478754</v>
+        <v>10.84497634802411</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907181149417</v>
+        <v>37.78907199699578</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.885176576332128</v>
+        <v>5.508586368528853</v>
       </c>
       <c r="C2" t="n">
-        <v>7.435757111965342</v>
+        <v>4.515057691831081</v>
       </c>
       <c r="D2" t="n">
-        <v>35.05624702324511</v>
+        <v>30.57162351024567</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.43860454408685</v>
+        <v>15.33489914033518</v>
       </c>
       <c r="C3" t="n">
-        <v>23.69448084199677</v>
+        <v>16.85660808191773</v>
       </c>
       <c r="D3" t="n">
-        <v>59.3908273684108</v>
+        <v>94.93009426214533</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.22059980048183</v>
+        <v>31.66430870507238</v>
       </c>
       <c r="C4" t="n">
-        <v>67.06809441562085</v>
+        <v>62.53732876052182</v>
       </c>
       <c r="D4" t="n">
-        <v>70.84585958156258</v>
+        <v>118.2466022380071</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.54051068334605</v>
+        <v>38.43542262126263</v>
       </c>
       <c r="C5" t="n">
-        <v>102.1508486268806</v>
+        <v>102.641722479004</v>
       </c>
       <c r="D5" t="n">
-        <v>53.57888095926969</v>
+        <v>79.93880681829654</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.31328499530853</v>
+        <v>36.30699359845555</v>
       </c>
       <c r="C6" t="n">
-        <v>123.9348484364131</v>
+        <v>111.6983450506809</v>
       </c>
       <c r="D6" t="n">
-        <v>40.49316580936395</v>
+        <v>50.59633143376788</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.3919226226395</v>
+        <v>25.57158245251667</v>
       </c>
       <c r="C7" t="n">
-        <v>134.7448724078747</v>
+        <v>85.87739868128548</v>
       </c>
       <c r="D7" t="n">
-        <v>37.84833749412304</v>
+        <v>39.82459562277186</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.60211444233956</v>
+        <v>13.76901155206151</v>
       </c>
       <c r="C8" t="n">
-        <v>100.5555086074795</v>
+        <v>48.40016181936775</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>36.38356991938679</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>53.47187045950676</v>
+        <v>31.39530983410874</v>
       </c>
       <c r="D9" t="n">
         <v>34.50155957034565</v>
@@ -895,10 +895,10 @@
         <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
         <v>36.42774856607789</v>
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>27.98864530037232</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.685043487975346</v>
+        <v>7.700132964926667</v>
       </c>
       <c r="C21" t="n">
-        <v>93.18115229170107</v>
+        <v>94.32662882035167</v>
       </c>
       <c r="D21" t="n">
-        <v>8.645673923972264</v>
+        <v>8.6626495855425</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.465389469541994</v>
+        <v>6.342090169434394</v>
       </c>
       <c r="C2" t="n">
-        <v>8.374307917225291</v>
+        <v>5.407466354991432</v>
       </c>
       <c r="D2" t="n">
-        <v>31.67903492063608</v>
+        <v>29.70768553050848</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.9758004647591</v>
+        <v>16.83206438931157</v>
       </c>
       <c r="C3" t="n">
-        <v>26.24211613451724</v>
+        <v>17.13640617762807</v>
       </c>
       <c r="D3" t="n">
-        <v>71.15707360380883</v>
+        <v>96.42725951112172</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.16954891986099</v>
+        <v>30.18383316706819</v>
       </c>
       <c r="C4" t="n">
-        <v>63.04783756673017</v>
+        <v>52.07189823325082</v>
       </c>
       <c r="D4" t="n">
-        <v>82.31954500109505</v>
+        <v>134.4935449955875</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.27744335633691</v>
+        <v>42.55876297909924</v>
       </c>
       <c r="C5" t="n">
-        <v>111.4038207394068</v>
+        <v>107.7958979262998</v>
       </c>
       <c r="D5" t="n">
-        <v>64.13266877992289</v>
+        <v>101.5618000043326</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.0944373727195</v>
+        <v>44.07556318216056</v>
       </c>
       <c r="C6" t="n">
-        <v>142.3701068267597</v>
+        <v>136.6543716926348</v>
       </c>
       <c r="D6" t="n">
-        <v>47.21519234034186</v>
+        <v>61.78629176677302</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.49468733641593</v>
+        <v>33.83593462686632</v>
       </c>
       <c r="C7" t="n">
-        <v>155.2260930138717</v>
+        <v>121.1506119471691</v>
       </c>
       <c r="D7" t="n">
-        <v>40.36357511240336</v>
+        <v>44.97484407925062</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.86075605691297</v>
+        <v>20.27799883121787</v>
       </c>
       <c r="C8" t="n">
-        <v>138.1073582949201</v>
+        <v>79.77681844709581</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>10.53906160508951</v>
       </c>
       <c r="C9" t="n">
-        <v>85.86561770883451</v>
+        <v>44.92968368485526</v>
       </c>
       <c r="D9" t="n">
-        <v>35.61093447614454</v>
+        <v>36.16562192904399</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>47.11898106532567</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>31.8076438698924</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>30.8092064546734</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.86496720303333</v>
+        <v>7.883758687894718</v>
       </c>
       <c r="C21" t="n">
-        <v>101.2614527390541</v>
+        <v>103.4743327786182</v>
       </c>
       <c r="D21" t="n">
-        <v>9.831209003791662</v>
+        <v>9.854698359868397</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.439283192154829</v>
+        <v>6.524695242424301</v>
       </c>
       <c r="C2" t="n">
-        <v>13.26930197059989</v>
+        <v>7.6026542216873</v>
       </c>
       <c r="D2" t="n">
-        <v>32.008902149263</v>
+        <v>25.88083297935441</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.79908587799467</v>
+        <v>18.6384801651257</v>
       </c>
       <c r="C3" t="n">
-        <v>29.01064466049325</v>
+        <v>18.8839170911874</v>
       </c>
       <c r="D3" t="n">
-        <v>78.33855806037424</v>
+        <v>96.7708712076081</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.53592073999429</v>
+        <v>30.47737573063798</v>
       </c>
       <c r="C4" t="n">
-        <v>64.01780429852602</v>
+        <v>47.59218345877263</v>
       </c>
       <c r="D4" t="n">
-        <v>93.80599314078273</v>
+        <v>148.2517573229024</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.46183199828607</v>
+        <v>43.95775345765094</v>
       </c>
       <c r="C5" t="n">
-        <v>112.1646752101981</v>
+        <v>101.19364461524</v>
       </c>
       <c r="D5" t="n">
-        <v>75.12824306748718</v>
+        <v>120.1168316145973</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.02401357992099</v>
+        <v>49.67054334866313</v>
       </c>
       <c r="C6" t="n">
-        <v>157.7059877147991</v>
+        <v>152.3122658276672</v>
       </c>
       <c r="D6" t="n">
-        <v>54.90325861229863</v>
+        <v>76.03537794621123</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>43.35790561035613</v>
+        <v>41.80085375142069</v>
       </c>
       <c r="C7" t="n">
-        <v>176.3660663294182</v>
+        <v>153.7289277648953</v>
       </c>
       <c r="D7" t="n">
-        <v>43.59745205019235</v>
+        <v>50.48441219548373</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.12078032981814</v>
+        <v>27.28767743954009</v>
       </c>
       <c r="C8" t="n">
-        <v>167.3143524962627</v>
+        <v>114.658314378985</v>
       </c>
       <c r="D8" t="n">
-        <v>40.13875488813084</v>
+        <v>41.30703465618455</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.19999879422586</v>
+        <v>14.8656237377052</v>
       </c>
       <c r="C9" t="n">
-        <v>123.1406145436774</v>
+        <v>68.78124415953151</v>
       </c>
       <c r="D9" t="n">
-        <v>36.72030938194344</v>
+        <v>37.27499683484289</v>
       </c>
     </row>
     <row r="10">
@@ -1514,10 +1514,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.687084524252525</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>69.46846755250431</v>
+        <v>42.27896488338889</v>
       </c>
       <c r="D10" t="n">
         <v>36.30012136452581</v>
@@ -1531,10 +1531,10 @@
         <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>42.11403126907541</v>
+        <v>35.36157055926586</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>36.01639627799849</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>28.27040689149115</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.029489328835352</v>
+        <v>8.052836259804591</v>
       </c>
       <c r="C21" t="n">
-        <v>109.4017921053817</v>
+        <v>111.7331031047887</v>
       </c>
       <c r="D21" t="n">
-        <v>11.04054782714861</v>
+        <v>11.07264985723131</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.947427592327178</v>
+        <v>5.98964274360979</v>
       </c>
       <c r="C2" t="n">
-        <v>9.022261402028187</v>
+        <v>5.108033305196154</v>
       </c>
       <c r="D2" t="n">
-        <v>26.20873671257285</v>
+        <v>21.24011158137974</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.53601855098553</v>
+        <v>22.0549621759046</v>
       </c>
       <c r="C3" t="n">
-        <v>45.97524498987813</v>
+        <v>30.19855938263188</v>
       </c>
       <c r="D3" t="n">
-        <v>83.27674901273569</v>
+        <v>107.1872143496668</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.23640557474101</v>
+        <v>21.10953913671491</v>
       </c>
       <c r="C4" t="n">
-        <v>91.01095742679206</v>
+        <v>77.46971134211582</v>
       </c>
       <c r="D4" t="n">
-        <v>88.22868443295661</v>
+        <v>140.7728033119502</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.99868376159304</v>
+        <v>27.9798095710341</v>
       </c>
       <c r="C5" t="n">
-        <v>94.22323591508764</v>
+        <v>91.00801218367933</v>
       </c>
       <c r="D5" t="n">
-        <v>52.98983233672161</v>
+        <v>78.85888434362505</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.88810612391165</v>
+        <v>25.92206638293279</v>
       </c>
       <c r="C6" t="n">
-        <v>116.1662788527081</v>
+        <v>101.2329145234099</v>
       </c>
       <c r="D6" t="n">
-        <v>28.69943063824701</v>
+        <v>33.24786775202249</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.96598298771663</v>
+        <v>18.08575620763474</v>
       </c>
       <c r="C7" t="n">
-        <v>117.6173019595849</v>
+        <v>80.6073770048886</v>
       </c>
       <c r="D7" t="n">
-        <v>28.20659329071511</v>
+        <v>29.04500583014188</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.846929473595507</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C8" t="n">
-        <v>90.70857913388404</v>
+        <v>50.65327280061418</v>
       </c>
       <c r="D8" t="n">
-        <v>27.03733177495716</v>
+        <v>27.45457454926205</v>
       </c>
     </row>
     <row r="9">
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>53.0281204971872</v>
+        <v>32.28280975874785</v>
       </c>
       <c r="D9" t="n">
         <v>27.62343515439249</v>
@@ -1828,10 +1828,10 @@
         <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>27.75891633757857</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>28.89774367450487</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>28.78680618392497</v>
+        <v>28.60910984945629</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>26.90381408717959</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>23.96838845148163</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>17.9443845382232</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>74.64718669240621</v>
       </c>
       <c r="D20" t="n">
         <v>7.397468951499714</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.723769042208152</v>
+        <v>3.684499134038279</v>
       </c>
       <c r="C2" t="n">
-        <v>4.311835917051991</v>
+        <v>2.917754177021521</v>
       </c>
       <c r="D2" t="n">
-        <v>19.01252604044373</v>
+        <v>15.51063197939536</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.18749811597792</v>
+        <v>22.03532722181966</v>
       </c>
       <c r="C3" t="n">
-        <v>41.35612204139689</v>
+        <v>25.40763058590746</v>
       </c>
       <c r="D3" t="n">
-        <v>84.97517254108267</v>
+        <v>100.8745766113598</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.45559735469531</v>
+        <v>30.40079940970673</v>
       </c>
       <c r="C4" t="n">
-        <v>104.8712715153485</v>
+        <v>78.58006799561895</v>
       </c>
       <c r="D4" t="n">
-        <v>106.9388321804923</v>
+        <v>160.3763414703505</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.82749980815561</v>
+        <v>31.21957699504858</v>
       </c>
       <c r="C5" t="n">
-        <v>130.1306581979147</v>
+        <v>117.9569866652543</v>
       </c>
       <c r="D5" t="n">
-        <v>66.95519342963247</v>
+        <v>101.9054117008189</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.16107304342126</v>
+        <v>31.11452999069417</v>
       </c>
       <c r="C6" t="n">
-        <v>136.4933650691383</v>
+        <v>124.4178683069026</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>43.02902012943346</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.94791061841269</v>
+        <v>17.0676838383308</v>
       </c>
       <c r="C7" t="n">
-        <v>141.3922861133299</v>
+        <v>106.0591862374872</v>
       </c>
       <c r="D7" t="n">
-        <v>30.60205768907732</v>
+        <v>31.85967649821749</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.344855486097888</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
-        <v>116.5776311407875</v>
+        <v>69.09540342489051</v>
       </c>
       <c r="D8" t="n">
-        <v>28.20561154301086</v>
+        <v>28.62285431731576</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>4.659374604355361</v>
       </c>
       <c r="C9" t="n">
-        <v>58.3531200450219</v>
+        <v>37.71874679716245</v>
       </c>
       <c r="D9" t="n">
         <v>28.6218725696115</v>
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>35.01894061048373</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
         <v>28.42257778564941</v>
@@ -2181,7 +2181,7 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
         <v>25.23582473766426</v>
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
         <v>15.29268398905256</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>64.99562501195582</v>
       </c>
       <c r="D19" t="n">
         <v>6.018113427032947</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.449280595646544</v>
+        <v>3.679590395517045</v>
       </c>
       <c r="C2" t="n">
-        <v>5.580253950938871</v>
+        <v>5.89441321629785</v>
       </c>
       <c r="D2" t="n">
-        <v>20.84839424738527</v>
+        <v>15.54597489674824</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.55364895193297</v>
+        <v>17.18549356284042</v>
       </c>
       <c r="C3" t="n">
-        <v>28.42159603794516</v>
+        <v>17.89235190989812</v>
       </c>
       <c r="D3" t="n">
-        <v>81.39670215910306</v>
+        <v>90.57604319381073</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.01188845010475</v>
+        <v>36.52690508420682</v>
       </c>
       <c r="C4" t="n">
-        <v>103.9778811044839</v>
+        <v>70.69270693970007</v>
       </c>
       <c r="D4" t="n">
-        <v>122.279621807053</v>
+        <v>173.1007734650933</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.33157834879072</v>
+        <v>38.09181092477625</v>
       </c>
       <c r="C5" t="n">
-        <v>161.0557108816893</v>
+        <v>131.4069302134356</v>
       </c>
       <c r="D5" t="n">
-        <v>86.22199212547613</v>
+        <v>132.4868526881071</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.20511282139213</v>
+        <v>36.74976181307086</v>
       </c>
       <c r="C6" t="n">
-        <v>171.1902924326291</v>
+        <v>156.1764247915826</v>
       </c>
       <c r="D6" t="n">
-        <v>45.12210623488766</v>
+        <v>61.50453017565419</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.21226279276233</v>
+        <v>25.15237618280328</v>
       </c>
       <c r="C7" t="n">
-        <v>169.2994463542497</v>
+        <v>141.8713789930023</v>
       </c>
       <c r="D7" t="n">
-        <v>33.17718191731671</v>
+        <v>36.23139902522853</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.18348900970292</v>
+        <v>12.60073178400781</v>
       </c>
       <c r="C8" t="n">
-        <v>149.957053085179</v>
+        <v>102.0575825949772</v>
       </c>
       <c r="D8" t="n">
-        <v>29.70768553050848</v>
+        <v>30.70906818884022</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>94.85155444580556</v>
+        <v>58.68593251676156</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>29.39843500367073</v>
       </c>
     </row>
     <row r="10">
@@ -2450,7 +2450,7 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>49.25428232206248</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
         <v>30.60598467989432</v>
@@ -2464,7 +2464,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>34.47308888692249</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
         <v>30.03068052520567</v>
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>26.25291535926396</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.47158305540374</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.97365704290136</v>
       </c>
     </row>
     <row r="15">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>35.50686921949439</v>
       </c>
       <c r="D19" t="n">
         <v>4.212679398923063</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.634029090494193</v>
+        <v>2.164753687864217</v>
       </c>
       <c r="C2" t="n">
-        <v>2.611448893296516</v>
+        <v>2.659554530804609</v>
       </c>
       <c r="D2" t="n">
-        <v>14.55048272464198</v>
+        <v>10.74817386609408</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.0199791114502</v>
+        <v>16.85660808191773</v>
       </c>
       <c r="C3" t="n">
-        <v>27.38094347144354</v>
+        <v>21.3628300444106</v>
       </c>
       <c r="D3" t="n">
-        <v>81.94648087348126</v>
+        <v>86.96321164218247</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.94280625790898</v>
+        <v>40.30467025014855</v>
       </c>
       <c r="C4" t="n">
-        <v>101.9741340401162</v>
+        <v>68.3316037109865</v>
       </c>
       <c r="D4" t="n">
-        <v>132.5791369723063</v>
+        <v>182.136779334981</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.90237467558562</v>
+        <v>39.88350048502668</v>
       </c>
       <c r="C5" t="n">
-        <v>195.2450746820845</v>
+        <v>151.066427990978</v>
       </c>
       <c r="D5" t="n">
-        <v>91.67069188404594</v>
+        <v>143.6296891313084</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.55729820530948</v>
+        <v>30.87302005544945</v>
       </c>
       <c r="C6" t="n">
-        <v>206.0482264196164</v>
+        <v>190.3500806287099</v>
       </c>
       <c r="D6" t="n">
-        <v>44.80009298789471</v>
+        <v>59.93471559656354</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.024805734513427</v>
+        <v>8.324238784308704</v>
       </c>
       <c r="C7" t="n">
-        <v>185.5886042631128</v>
+        <v>143.9674103415693</v>
       </c>
       <c r="D7" t="n">
-        <v>33.53650157707104</v>
+        <v>36.23139902522853</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>115.4093513727338</v>
+        <v>76.18853058807372</v>
       </c>
       <c r="D8" t="n">
-        <v>31.37665662772806</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>37.60780930658255</v>
+        <v>28.73281006019139</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="D10" t="n">
         <v>23.48831382410494</v>
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.96816746730337</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.97067074205961</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.82875929330033</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>9.506263020221864</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>28.80545939030567</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>30.49799243242716</v>
       </c>
       <c r="D18" t="n">
         <v>3.21031499288707</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.491094836301658</v>
+        <v>2.667408512438584</v>
       </c>
       <c r="C2" t="n">
-        <v>5.62345084992573</v>
+        <v>6.141813637768045</v>
       </c>
       <c r="D2" t="n">
-        <v>13.34784178693963</v>
+        <v>18.13386184514283</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.6806542586793</v>
+        <v>12.25221134900019</v>
       </c>
       <c r="C3" t="n">
-        <v>18.62375394956199</v>
+        <v>15.58033606639688</v>
       </c>
       <c r="D3" t="n">
-        <v>75.97254609313943</v>
+        <v>76.60086462385738</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.89251614081414</v>
+        <v>36.56519324467246</v>
       </c>
       <c r="C4" t="n">
-        <v>85.3698351181899</v>
+        <v>61.2993449054666</v>
       </c>
       <c r="D4" t="n">
-        <v>140.9004305135022</v>
+        <v>183.7704075148477</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.0999680060465</v>
+        <v>49.1119289049467</v>
       </c>
       <c r="C5" t="n">
-        <v>193.4288414292279</v>
+        <v>140.2917469368692</v>
       </c>
       <c r="D5" t="n">
-        <v>112.3855684436536</v>
+        <v>170.9959063871882</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.0629803884546</v>
+        <v>40.45291415348983</v>
       </c>
       <c r="C6" t="n">
-        <v>254.3502134685594</v>
+        <v>215.1853523030414</v>
       </c>
       <c r="D6" t="n">
-        <v>58.36490101747288</v>
+        <v>85.01149720613982</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.54677671800324</v>
+        <v>17.84620976779852</v>
       </c>
       <c r="C7" t="n">
-        <v>237.7498415374501</v>
+        <v>204.0336801305018</v>
       </c>
       <c r="D7" t="n">
-        <v>37.72856427420492</v>
+        <v>42.57937968088841</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.257258956241669</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>169.4840149226481</v>
+        <v>123.9211039685536</v>
       </c>
       <c r="D8" t="n">
-        <v>32.96217917008666</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>76.10311853780424</v>
+        <v>53.69374544066654</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>33.17030968338697</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>33.88011327355743</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>25.0542014123786</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.1456838753228</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>34.47210713921825</v>
       </c>
       <c r="D17" t="n">
         <v>4.722206457427158</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.316924582022473</v>
+        <v>1.834886459237289</v>
       </c>
       <c r="C2" t="n">
-        <v>2.922662915542754</v>
+        <v>3.390956570468483</v>
       </c>
       <c r="D2" t="n">
-        <v>9.868527923088937</v>
+        <v>14.43267300013236</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.04251825091887</v>
+        <v>11.14774518172253</v>
       </c>
       <c r="C3" t="n">
-        <v>20.48907458763093</v>
+        <v>19.67422399310608</v>
       </c>
       <c r="D3" t="n">
-        <v>70.73001335246146</v>
+        <v>74.12195167063418</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.9488356128547</v>
+        <v>32.08547847019426</v>
       </c>
       <c r="C4" t="n">
-        <v>70.33535077535424</v>
+        <v>53.00357680458105</v>
       </c>
       <c r="D4" t="n">
-        <v>145.5715860903086</v>
+        <v>182.0091521334289</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.34602682691395</v>
+        <v>53.38253141842033</v>
       </c>
       <c r="C5" t="n">
-        <v>186.1393647251953</v>
+        <v>134.352173326176</v>
       </c>
       <c r="D5" t="n">
-        <v>129.3943474197296</v>
+        <v>190.0908992347887</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.79129831628549</v>
+        <v>47.81896717845365</v>
       </c>
       <c r="C6" t="n">
-        <v>284.3779487506524</v>
+        <v>228.9111669561161</v>
       </c>
       <c r="D6" t="n">
-        <v>69.6756163181004</v>
+        <v>102.5209675113817</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.81006502919063</v>
+        <v>17.36711688812607</v>
       </c>
       <c r="C7" t="n">
-        <v>288.4139135628109</v>
+        <v>247.5113589607761</v>
       </c>
       <c r="D7" t="n">
-        <v>42.39971985101125</v>
+        <v>48.80758711663017</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.339324852770902</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>212.4600206760522</v>
+        <v>162.6412334240478</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>87.52968006753285</v>
+        <v>65.45311944213483</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>34.16482010778901</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>25.76596849795754</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>24.16670148773948</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.70640068316797</v>
+        <v>18.00819813899924</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>3.719842051391165</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.96095107600838</v>
+        <v>2.957024085191393</v>
       </c>
       <c r="C2" t="n">
-        <v>5.618542111404496</v>
+        <v>9.12632665867835</v>
       </c>
       <c r="D2" t="n">
-        <v>16.71818165561893</v>
+        <v>17.11480772813465</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.53906160508951</v>
+        <v>8.771915737445251</v>
       </c>
       <c r="C3" t="n">
-        <v>16.27246819789088</v>
+        <v>16.4344565690916</v>
       </c>
       <c r="D3" t="n">
-        <v>63.63197745075702</v>
+        <v>69.71881321708723</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.48188355853172</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="C4" t="n">
-        <v>61.65670106981243</v>
+        <v>51.07640606114455</v>
       </c>
       <c r="D4" t="n">
-        <v>146.6564173035013</v>
+        <v>176.2659280635851</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.19247327442395</v>
+        <v>51.93445355465628</v>
       </c>
       <c r="C5" t="n">
-        <v>161.742934274662</v>
+        <v>117.8588118948296</v>
       </c>
       <c r="D5" t="n">
-        <v>145.6913593102267</v>
+        <v>207.3205714443202</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.08943082320704</v>
+        <v>56.79508643838223</v>
       </c>
       <c r="C6" t="n">
-        <v>289.9729289171549</v>
+        <v>223.4369417572358</v>
       </c>
       <c r="D6" t="n">
-        <v>86.54106012935635</v>
+        <v>129.288318667671</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.06307819944583</v>
+        <v>31.56024344842221</v>
       </c>
       <c r="C7" t="n">
-        <v>338.4192328786222</v>
+        <v>286.317882214244</v>
       </c>
       <c r="D7" t="n">
-        <v>48.74770050667112</v>
+        <v>61.50354842794993</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>9.012443924985718</v>
       </c>
       <c r="C8" t="n">
-        <v>281.2216298814988</v>
+        <v>228.6490403190821</v>
       </c>
       <c r="D8" t="n">
-        <v>36.88426124855267</v>
+        <v>39.47116644924301</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>151.3187371509693</v>
+        <v>117.7046775052628</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>33.9468721174462</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>57.36842709766236</v>
+        <v>48.11545498513618</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>27.3318560862312</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>24.87748682561417</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>11.98419422574081</v>
+      </c>
+      <c r="D14" t="n">
         <v>11.67690719431156</v>
-      </c>
-      <c r="D14" t="n">
-        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.41982816451914</v>
+        <v>4.713370728088937</v>
       </c>
       <c r="C2" t="n">
-        <v>11.56793319914017</v>
+        <v>3.051271864799086</v>
       </c>
       <c r="D2" t="n">
-        <v>6.674902641174064</v>
+        <v>7.071528713689775</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.118611545764617</v>
+        <v>2.092104357749953</v>
       </c>
       <c r="C2" t="n">
-        <v>3.235840433197487</v>
+        <v>5.110978548308895</v>
       </c>
       <c r="D2" t="n">
-        <v>12.30424397732527</v>
+        <v>12.59680479319083</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.95063487734718</v>
+        <v>12.0656792851933</v>
       </c>
       <c r="C3" t="n">
-        <v>20.19455027635689</v>
+        <v>24.83330817892307</v>
       </c>
       <c r="D3" t="n">
-        <v>70.22441328477434</v>
+        <v>76.31124905110458</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.82794177651211</v>
+        <v>38.61999118966102</v>
       </c>
       <c r="C4" t="n">
-        <v>89.49219372832225</v>
+        <v>72.18594519785947</v>
       </c>
       <c r="D4" t="n">
-        <v>149.1068595733013</v>
+        <v>183.8980347163998</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.77841242294326</v>
+        <v>33.89483948912113</v>
       </c>
       <c r="C5" t="n">
-        <v>244.185197738788</v>
+        <v>182.212373908208</v>
       </c>
       <c r="D5" t="n">
-        <v>130.744250513069</v>
+        <v>189.8700060013331</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.6365166697172</v>
+        <v>19.56230475482195</v>
       </c>
       <c r="C6" t="n">
-        <v>279.7087566692545</v>
+        <v>236.7602398515693</v>
       </c>
       <c r="D6" t="n">
-        <v>70.3196428120863</v>
+        <v>98.17378867697681</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.389794896314989</v>
+        <v>5.928774385946488</v>
       </c>
       <c r="C7" t="n">
-        <v>197.745586084801</v>
+        <v>160.7955477400638</v>
       </c>
       <c r="D7" t="n">
-        <v>32.09922293805371</v>
+        <v>36.17151241526948</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>1.752419652080557</v>
       </c>
       <c r="C8" t="n">
-        <v>111.4872692942678</v>
+        <v>86.70304850055705</v>
       </c>
       <c r="D8" t="n">
-        <v>24.53387512912779</v>
+        <v>24.95111790343269</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>43.70937128847648</v>
+        <v>36.72030938194344</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>20.85624822901923</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.34948648717864</v>
+        <v>22.49183990429443</v>
       </c>
       <c r="D10" t="n">
-        <v>19.50241814486289</v>
+        <v>19.07535789351553</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.81497376771187</v>
+        <v>16.8811517745239</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>16.52575910558656</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>9.886199381765381</v>
+      </c>
+      <c r="D13" t="n">
         <v>9.626036240139976</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
         <v>2.5083653843506</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.238024912784233</v>
+        <v>5.850234569606743</v>
       </c>
       <c r="C2" t="n">
-        <v>7.561420818108934</v>
+        <v>4.468915549731481</v>
       </c>
       <c r="D2" t="n">
-        <v>8.19955682586936</v>
+        <v>20.62848276163398</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.395325529641976</v>
+        <v>10.0187353218387</v>
       </c>
       <c r="C3" t="n">
-        <v>29.1480893390878</v>
+        <v>7.809802987283376</v>
       </c>
       <c r="D3" t="n">
-        <v>8.742463306317847</v>
+        <v>9.360964359993337</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4557,7 +4557,7 @@
         <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>24.19517217116264</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39811134327514</v>
+        <v>13.39945745800067</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14305350302867</v>
+        <v>70.1501008095329</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576248393326487</v>
+        <v>1.576406759764784</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.315762907868979</v>
+        <v>4.158683275189489</v>
       </c>
       <c r="C2" t="n">
-        <v>4.607341976030281</v>
+        <v>5.867906028283186</v>
       </c>
       <c r="D2" t="n">
-        <v>14.39733008277947</v>
+        <v>27.04125876577415</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.64553232550467</v>
+        <v>16.11538856521139</v>
       </c>
       <c r="C3" t="n">
-        <v>29.35916509550086</v>
+        <v>13.93099992326224</v>
       </c>
       <c r="D3" t="n">
-        <v>13.51375714895735</v>
+        <v>24.42588288166064</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.03975293425538</v>
+        <v>11.74170254279185</v>
       </c>
       <c r="C4" t="n">
-        <v>44.95030038664446</v>
+        <v>12.63509295365645</v>
       </c>
       <c r="D4" t="n">
-        <v>19.65458903902115</v>
+        <v>19.97365704290135</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.043417883165113</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.424156065963628</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
         <v>29.10881943091793</v>
@@ -4879,10 +4879,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
         <v>34.77743067523902</v>
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
@@ -4924,7 +4924,7 @@
         <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4938,7 +4938,7 @@
         <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.5049467818149</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44115279672366</v>
+        <v>15.44485546761624</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14537876066886</v>
+        <v>86.16603576670116</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250769009836561</v>
+        <v>3.251548519498157</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.986877426946297</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C2" t="n">
-        <v>5.159084185816988</v>
+        <v>8.552985999398212</v>
       </c>
       <c r="D2" t="n">
-        <v>19.77730750205199</v>
+        <v>32.3633130704961</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.68832831386403</v>
+        <v>15.15327581504952</v>
       </c>
       <c r="C3" t="n">
-        <v>22.42802630351838</v>
+        <v>19.3306122966197</v>
       </c>
       <c r="D3" t="n">
-        <v>21.89297380470387</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.04947260030661</v>
+        <v>22.69211643596077</v>
       </c>
       <c r="C4" t="n">
-        <v>61.78432827136452</v>
+        <v>25.72964383290041</v>
       </c>
       <c r="D4" t="n">
-        <v>22.02845498788993</v>
+        <v>27.72062817711294</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.01382658331747</v>
+        <v>10.75013736150258</v>
       </c>
       <c r="C5" t="n">
-        <v>49.62734644967627</v>
+        <v>15.56070111231195</v>
       </c>
       <c r="D5" t="n">
-        <v>29.52606220522283</v>
+        <v>29.62423697564751</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.876741757621407</v>
       </c>
       <c r="C6" t="n">
-        <v>12.11574841810989</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
         <v>36.6290068454485</v>
@@ -5204,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
@@ -5232,10 +5232,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
         <v>41.26874649571891</v>
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
         <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5288,10 +5288,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="C14" t="n">
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5347,7 +5347,7 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
         <v>37.30543101367455</v>
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73398973412051</v>
+        <v>16.74244024856455</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0773373781351</v>
+        <v>102.1288855162437</v>
       </c>
       <c r="D21" t="n">
-        <v>5.020196920236154</v>
+        <v>5.022732074569364</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.303802008968769</v>
+        <v>4.58279828342411</v>
       </c>
       <c r="C2" t="n">
-        <v>5.834526606338795</v>
+        <v>5.849252821902496</v>
       </c>
       <c r="D2" t="n">
-        <v>24.77342156896401</v>
+        <v>33.78390199854124</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.57895340806514</v>
+        <v>14.85875150377547</v>
       </c>
       <c r="C3" t="n">
-        <v>21.02903582496668</v>
+        <v>27.47911824186822</v>
       </c>
       <c r="D3" t="n">
-        <v>32.05406254365836</v>
+        <v>55.99888905023806</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.13354304997335</v>
+        <v>26.21462719879833</v>
       </c>
       <c r="C4" t="n">
-        <v>58.63193639302801</v>
+        <v>38.60722846950582</v>
       </c>
       <c r="D4" t="n">
-        <v>27.72062817711294</v>
+        <v>40.70031457496002</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.16295442337175</v>
+        <v>22.65382827549515</v>
       </c>
       <c r="C5" t="n">
-        <v>83.96397240570847</v>
+        <v>33.13398501832986</v>
       </c>
       <c r="D5" t="n">
-        <v>30.55689729468198</v>
+        <v>33.03581024790518</v>
       </c>
     </row>
     <row r="6">
@@ -5501,10 +5501,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.861655689159212</v>
+        <v>10.22392059202629</v>
       </c>
       <c r="C6" t="n">
-        <v>47.21519234034186</v>
+        <v>18.8377749490878</v>
       </c>
       <c r="D6" t="n">
         <v>38.15856976866503</v>
@@ -5515,10 +5515,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="D7" t="n">
         <v>39.46527596301753</v>
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.87734795689393</v>
       </c>
       <c r="D8" t="n">
         <v>40.38910055271378</v>
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.87187407682917</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>34.16874709860598</v>
       </c>
       <c r="D9" t="n">
-        <v>42.3781214015178</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.71459882216721</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>47.29864089520282</v>
       </c>
     </row>
     <row r="13">
@@ -5599,10 +5599,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>37.77765165941727</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05806134647355</v>
+        <v>18.07349467301713</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8073525936608</v>
+        <v>117.9080366763498</v>
       </c>
       <c r="D21" t="n">
-        <v>6.879261465323257</v>
+        <v>6.885140827816048</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.614034283510762</v>
+        <v>5.692173189223006</v>
       </c>
       <c r="C2" t="n">
-        <v>8.561821728736433</v>
+        <v>8.016951752879454</v>
       </c>
       <c r="D2" t="n">
-        <v>22.17179015270996</v>
+        <v>32.63427543686822</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.50317890838888</v>
+        <v>13.71992416684918</v>
       </c>
       <c r="C3" t="n">
-        <v>20.63633674326795</v>
+        <v>23.24778563656447</v>
       </c>
       <c r="D3" t="n">
-        <v>41.1548637620263</v>
+        <v>65.11932522269093</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.06299608398782</v>
+        <v>20.25443688631594</v>
       </c>
       <c r="C4" t="n">
-        <v>46.22657240216531</v>
+        <v>46.77536936883928</v>
       </c>
       <c r="D4" t="n">
-        <v>32.3024447128328</v>
+        <v>50.82115165804039</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.41406085148068</v>
+        <v>19.04590546238812</v>
       </c>
       <c r="C5" t="n">
-        <v>71.52032025438015</v>
+        <v>40.15348110369455</v>
       </c>
       <c r="D5" t="n">
-        <v>26.92443078896878</v>
+        <v>32.64311116620645</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.82769543013807</v>
+        <v>11.3107153006275</v>
       </c>
       <c r="C6" t="n">
-        <v>62.51082157250717</v>
+        <v>24.59376173908685</v>
       </c>
       <c r="D6" t="n">
-        <v>30.59125846433062</v>
+        <v>30.83276839957533</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.150248456478767</v>
+        <v>5.210135066437822</v>
       </c>
       <c r="C7" t="n">
-        <v>28.80545939030566</v>
+        <v>15.69029180927252</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -5843,7 +5843,7 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
         <v>30.37527396939631</v>
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>22.18749811597791</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5874,7 +5874,7 @@
         <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>32.32797015314322</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.081305133003238</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -5969,10 +5969,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.056727853065494</v>
+        <v>7.065948959722752</v>
       </c>
       <c r="C21" t="n">
-        <v>66.15682362248901</v>
+        <v>66.2432714974008</v>
       </c>
       <c r="D21" t="n">
-        <v>5.292545889799121</v>
+        <v>5.299461719792064</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.501714134599125</v>
+        <v>4.73398742987812</v>
       </c>
       <c r="C2" t="n">
-        <v>7.316965639751478</v>
+        <v>5.647012794827654</v>
       </c>
       <c r="D2" t="n">
-        <v>16.3755517068368</v>
+        <v>37.21118323406685</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.62651926622549</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="C3" t="n">
-        <v>28.9026524130261</v>
+        <v>28.55413197801848</v>
       </c>
       <c r="D3" t="n">
-        <v>49.8335134675681</v>
+        <v>77.47462008063705</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.74615361742335</v>
+        <v>24.38955821660351</v>
       </c>
       <c r="C4" t="n">
-        <v>49.74908316500287</v>
+        <v>54.19050977901544</v>
       </c>
       <c r="D4" t="n">
-        <v>46.0606570401476</v>
+        <v>74.29179402346888</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.72178985126644</v>
+        <v>26.04085785514665</v>
       </c>
       <c r="C5" t="n">
-        <v>79.52156404399165</v>
+        <v>68.94323253073227</v>
       </c>
       <c r="D5" t="n">
-        <v>33.1830724035422</v>
+        <v>44.76769531365456</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.8843180018149</v>
+        <v>19.84406634594078</v>
       </c>
       <c r="C6" t="n">
-        <v>93.26308666033425</v>
+        <v>48.02022545782425</v>
       </c>
       <c r="D6" t="n">
-        <v>32.4428346345401</v>
+        <v>34.41516577237194</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.701630813366979</v>
+        <v>10.00106386316226</v>
       </c>
       <c r="C7" t="n">
-        <v>65.27640485537042</v>
+        <v>27.5478405811655</v>
       </c>
       <c r="D7" t="n">
-        <v>33.29695513723482</v>
+        <v>33.65627479698915</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>30.29182541453534</v>
+        <v>20.27799883121787</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>32.46148784092078</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.28437234352885</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
         <v>32.97886888105885</v>
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.279171513620195</v>
+        <v>7.290486438529825</v>
       </c>
       <c r="C21" t="n">
-        <v>75.52140445380954</v>
+        <v>75.63879679974694</v>
       </c>
       <c r="D21" t="n">
-        <v>6.36927507441767</v>
+        <v>6.379175633713597</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.659775514982861</v>
+        <v>4.061490252469055</v>
       </c>
       <c r="C2" t="n">
-        <v>5.114905539125882</v>
+        <v>2.839214360681776</v>
       </c>
       <c r="D2" t="n">
-        <v>26.32752818478671</v>
+        <v>33.5816619714664</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.74294633240336</v>
+        <v>17.0971362694582</v>
       </c>
       <c r="C3" t="n">
-        <v>28.6424892714007</v>
+        <v>24.5633275602552</v>
       </c>
       <c r="D3" t="n">
-        <v>51.36994862471436</v>
+        <v>89.26541000864124</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.67631066170159</v>
+        <v>29.85200244303276</v>
       </c>
       <c r="C4" t="n">
-        <v>63.09888844735099</v>
+        <v>63.89017709697393</v>
       </c>
       <c r="D4" t="n">
-        <v>60.68673433801658</v>
+        <v>96.43511349275569</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.63115026730624</v>
+        <v>32.15223731408305</v>
       </c>
       <c r="C5" t="n">
-        <v>85.92746781420209</v>
+        <v>87.13010875190443</v>
       </c>
       <c r="D5" t="n">
-        <v>41.94517066394498</v>
+        <v>60.86835766330226</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.01515248838698</v>
+        <v>28.21641076775758</v>
       </c>
       <c r="C6" t="n">
-        <v>112.1411132652962</v>
+        <v>82.39513957432206</v>
       </c>
       <c r="D6" t="n">
-        <v>35.98498035146259</v>
+        <v>41.0164373357275</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.36711688812607</v>
+        <v>17.48689010804419</v>
       </c>
       <c r="C7" t="n">
-        <v>104.0829281088383</v>
+        <v>50.72395863531995</v>
       </c>
       <c r="D7" t="n">
-        <v>35.2133266559246</v>
+        <v>36.05173919535137</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>8.511752595819845</v>
       </c>
       <c r="C8" t="n">
-        <v>61.16779071309751</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D8" t="n">
-        <v>34.46425315758427</v>
+        <v>34.63115026730623</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>31.28437234352885</v>
+        <v>25.07187287105504</v>
       </c>
       <c r="D9" t="n">
         <v>32.8374972116473</v>
@@ -6496,7 +6496,7 @@
         <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6521,7 +6521,7 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
         <v>33.62976760897449</v>
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -6605,7 +6605,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.489415296720003</v>
+        <v>7.502138949161433</v>
       </c>
       <c r="C21" t="n">
-        <v>84.25592208810005</v>
+        <v>85.33683054671131</v>
       </c>
       <c r="D21" t="n">
-        <v>7.489415296720003</v>
+        <v>7.502138949161433</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_66_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_66_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497634802411</v>
+        <v>10.84497628750174</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907199699578</v>
+        <v>37.78907178610695</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.508586368528853</v>
+        <v>1.418625432636641</v>
       </c>
       <c r="C2" t="n">
-        <v>4.515057691831081</v>
+        <v>2.658572783100362</v>
       </c>
       <c r="D2" t="n">
-        <v>30.57162351024567</v>
+        <v>15.43209216305561</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.33489914033518</v>
+        <v>10.67159754516283</v>
       </c>
       <c r="C3" t="n">
-        <v>16.85660808191773</v>
+        <v>30.22310307523806</v>
       </c>
       <c r="D3" t="n">
-        <v>94.93009426214533</v>
+        <v>69.54700736884405</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.66430870507238</v>
+        <v>16.71916340332318</v>
       </c>
       <c r="C4" t="n">
-        <v>62.53732876052182</v>
+        <v>92.21065312138165</v>
       </c>
       <c r="D4" t="n">
-        <v>118.2466022380071</v>
+        <v>77.39313502118455</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.43542262126263</v>
+        <v>17.7450897542611</v>
       </c>
       <c r="C5" t="n">
-        <v>102.641722479004</v>
+        <v>96.38308086443064</v>
       </c>
       <c r="D5" t="n">
-        <v>79.93880681829654</v>
+        <v>48.91557936409734</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.30699359845555</v>
+        <v>13.12203981496287</v>
       </c>
       <c r="C6" t="n">
-        <v>111.6983450506809</v>
+        <v>58.08313942635406</v>
       </c>
       <c r="D6" t="n">
-        <v>50.59633143376788</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.57158245251667</v>
+        <v>6.707300315414209</v>
       </c>
       <c r="C7" t="n">
-        <v>85.87739868128548</v>
+        <v>37.24947139453248</v>
       </c>
       <c r="D7" t="n">
-        <v>39.82459562277186</v>
+        <v>29.40432548989622</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.76901155206151</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>48.40016181936775</v>
+        <v>28.95664853675967</v>
       </c>
       <c r="D8" t="n">
-        <v>36.38356991938679</v>
+        <v>31.12631096314512</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.432811868852599</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>31.39530983410874</v>
+        <v>32.28280975874785</v>
       </c>
       <c r="D9" t="n">
-        <v>34.50155957034565</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>29.32480392585223</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>38.43542262126263</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.700132964926667</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>94.32662882035167</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.6626495855425</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.342090169434394</v>
+        <v>1.571778074499143</v>
       </c>
       <c r="C2" t="n">
-        <v>5.407466354991432</v>
+        <v>4.039891802975625</v>
       </c>
       <c r="D2" t="n">
-        <v>29.70768553050848</v>
+        <v>15.57739082328414</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.83206438931157</v>
+        <v>7.539822368615503</v>
       </c>
       <c r="C3" t="n">
-        <v>17.13640617762807</v>
+        <v>18.45685683984004</v>
       </c>
       <c r="D3" t="n">
-        <v>96.42725951112172</v>
+        <v>66.4250496693392</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.18383316706819</v>
+        <v>19.08026663203676</v>
       </c>
       <c r="C4" t="n">
-        <v>52.07189823325082</v>
+        <v>82.7024266057513</v>
       </c>
       <c r="D4" t="n">
-        <v>134.4935449955875</v>
+        <v>93.1550944128671</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.55876297909924</v>
+        <v>21.72116795646068</v>
       </c>
       <c r="C5" t="n">
-        <v>107.7958979262998</v>
+        <v>138.819125380499</v>
       </c>
       <c r="D5" t="n">
-        <v>101.5618000043326</v>
+        <v>66.1207078810227</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.07556318216056</v>
+        <v>18.6365166697172</v>
       </c>
       <c r="C6" t="n">
-        <v>136.6543716926348</v>
+        <v>108.8807291394925</v>
       </c>
       <c r="D6" t="n">
-        <v>61.78629176677302</v>
+        <v>38.11831811279092</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.83593462686632</v>
+        <v>10.77958979262998</v>
       </c>
       <c r="C7" t="n">
-        <v>121.1506119471691</v>
+        <v>61.6832082578271</v>
       </c>
       <c r="D7" t="n">
-        <v>44.97484407925062</v>
+        <v>31.56024344842221</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.27799883121787</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>79.77681844709581</v>
+        <v>40.05530633326986</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>32.21114217633784</v>
       </c>
     </row>
     <row r="9">
@@ -1189,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.53906160508951</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>44.92968368485526</v>
+        <v>35.16718451382499</v>
       </c>
       <c r="D9" t="n">
         <v>36.16562192904399</v>
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>33.73775985644164</v>
+        <v>35.3036474447153</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>39.14718970684157</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>31.8076438698924</v>
+        <v>34.65078522139116</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.8092064546734</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>36.94316611080748</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.52772260099505</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.2949348885641</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>47.54309607356029</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.883758687894718</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103.4743327786182</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.854698359868397</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.524695242424301</v>
+        <v>0.8207410807503335</v>
       </c>
       <c r="C2" t="n">
-        <v>7.6026542216873</v>
+        <v>1.633628179866693</v>
       </c>
       <c r="D2" t="n">
-        <v>25.88083297935441</v>
+        <v>10.50960917396211</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.6384801651257</v>
+        <v>7.338564089244908</v>
       </c>
       <c r="C3" t="n">
-        <v>18.8839170911874</v>
+        <v>18.35377333089412</v>
       </c>
       <c r="D3" t="n">
-        <v>96.7708712076081</v>
+        <v>66.08143797285281</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.47737573063798</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="C4" t="n">
-        <v>47.59218345877263</v>
+        <v>75.70845596069702</v>
       </c>
       <c r="D4" t="n">
-        <v>148.2517573229024</v>
+        <v>103.9523556641735</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.95775345765094</v>
+        <v>22.50656611985813</v>
       </c>
       <c r="C5" t="n">
-        <v>101.19364461524</v>
+        <v>160.1966816404733</v>
       </c>
       <c r="D5" t="n">
-        <v>120.1168316145973</v>
+        <v>75.84001015306612</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.67054334866313</v>
+        <v>15.21512592041707</v>
       </c>
       <c r="C6" t="n">
-        <v>152.3122658276672</v>
+        <v>145.6707426084375</v>
       </c>
       <c r="D6" t="n">
-        <v>76.03537794621123</v>
+        <v>38.76234460677682</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.80085375142069</v>
+        <v>4.611268966847268</v>
       </c>
       <c r="C7" t="n">
-        <v>153.7289277648953</v>
+        <v>62.46173418729481</v>
       </c>
       <c r="D7" t="n">
-        <v>50.48441219548373</v>
+        <v>33.29695513723482</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.28767743954009</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>114.658314378985</v>
+        <v>40.38910055271378</v>
       </c>
       <c r="D8" t="n">
-        <v>41.30703465618455</v>
+        <v>36.38356991938679</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.8656237377052</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>68.78124415953151</v>
+        <v>26.95781021091316</v>
       </c>
       <c r="D9" t="n">
-        <v>37.27499683484289</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.971791358484101</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>42.27896488338889</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>35.36157055926586</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>33.1958351236974</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.69925071179776</v>
+        <v>17.95125677215293</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>28.27040689149115</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>14.05273663858884</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>43.44429940832985</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>41.1990424087174</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.052836259804591</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>111.7331031047887</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.07264985723131</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.98964274360979</v>
+        <v>0.8963356539773379</v>
       </c>
       <c r="C2" t="n">
-        <v>5.108033305196154</v>
+        <v>5.291620125890307</v>
       </c>
       <c r="D2" t="n">
-        <v>21.24011158137974</v>
+        <v>9.827294519510572</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.0549621759046</v>
+        <v>4.977460860531329</v>
       </c>
       <c r="C3" t="n">
-        <v>30.19855938263188</v>
+        <v>11.47663066264521</v>
       </c>
       <c r="D3" t="n">
-        <v>107.1872143496668</v>
+        <v>59.37119241432586</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.10953913671491</v>
+        <v>17.89333365760237</v>
       </c>
       <c r="C4" t="n">
-        <v>77.46971134211582</v>
+        <v>59.8061066473072</v>
       </c>
       <c r="D4" t="n">
-        <v>140.7728033119502</v>
+        <v>113.1670396162341</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.9798095710341</v>
+        <v>27.21895510024282</v>
       </c>
       <c r="C5" t="n">
-        <v>91.00801218367933</v>
+        <v>150.9682532205533</v>
       </c>
       <c r="D5" t="n">
-        <v>78.85888434362505</v>
+        <v>95.69585747145786</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.92206638293279</v>
+        <v>22.1786623866397</v>
       </c>
       <c r="C6" t="n">
-        <v>101.2329145234099</v>
+        <v>201.7412992410856</v>
       </c>
       <c r="D6" t="n">
-        <v>33.24786775202249</v>
+        <v>51.36111289537615</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.08575620763474</v>
+        <v>9.82140403328509</v>
       </c>
       <c r="C7" t="n">
-        <v>80.6073770048886</v>
+        <v>134.6849857979157</v>
       </c>
       <c r="D7" t="n">
-        <v>29.04500583014188</v>
+        <v>36.83026512481909</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.2641722479004</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>50.65327280061418</v>
+        <v>61.16779071309751</v>
       </c>
       <c r="D8" t="n">
-        <v>27.45457454926205</v>
+        <v>37.63529824230147</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>32.28280975874785</v>
+        <v>37.60780930658255</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>27.75891633757857</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>28.89774367450487</v>
+        <v>32.45657910239955</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>31.45225120095506</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>26.90381408717959</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>36.78510473042374</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>48.63872651149973</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>74.64718669240621</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.684499134038279</v>
+        <v>0.4388412237983242</v>
       </c>
       <c r="C2" t="n">
-        <v>2.917754177021521</v>
+        <v>2.669372007847077</v>
       </c>
       <c r="D2" t="n">
-        <v>15.51063197939536</v>
+        <v>7.258060777496669</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.03532722181966</v>
+        <v>4.177336481570179</v>
       </c>
       <c r="C3" t="n">
-        <v>25.40763058590746</v>
+        <v>16.51299638543135</v>
       </c>
       <c r="D3" t="n">
-        <v>100.8745766113598</v>
+        <v>54.55571992499526</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.40079940970673</v>
+        <v>14.89409442112836</v>
       </c>
       <c r="C4" t="n">
-        <v>78.58006799561895</v>
+        <v>45.89474167812989</v>
       </c>
       <c r="D4" t="n">
-        <v>160.3763414703505</v>
+        <v>117.1362455845039</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.21957699504858</v>
+        <v>28.86338250485623</v>
       </c>
       <c r="C5" t="n">
-        <v>117.9569866652543</v>
+        <v>138.0828146023139</v>
       </c>
       <c r="D5" t="n">
-        <v>101.9054117008189</v>
+        <v>111.0111216577081</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.11452999069417</v>
+        <v>27.25037102677872</v>
       </c>
       <c r="C6" t="n">
-        <v>124.4178683069026</v>
+        <v>229.1124252354867</v>
       </c>
       <c r="D6" t="n">
-        <v>43.02902012943346</v>
+        <v>62.87308647537424</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.0676838383308</v>
+        <v>11.31856928226148</v>
       </c>
       <c r="C7" t="n">
-        <v>106.0591862374872</v>
+        <v>194.0925028772986</v>
       </c>
       <c r="D7" t="n">
-        <v>31.85967649821749</v>
+        <v>41.26187426178919</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>69.09540342489051</v>
+        <v>93.79617566374026</v>
       </c>
       <c r="D8" t="n">
-        <v>28.62285431731576</v>
+        <v>40.13875488813084</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.659374604355361</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>37.71874679716245</v>
+        <v>49.58905828921062</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>42.04530892977813</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>31.17539834835746</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>41.33157834879071</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>64.99562501195582</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.679590395517045</v>
+        <v>0.5615596868291756</v>
       </c>
       <c r="C2" t="n">
-        <v>5.89441321629785</v>
+        <v>5.400594121061704</v>
       </c>
       <c r="D2" t="n">
-        <v>15.54597489674824</v>
+        <v>11.59640388256332</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.18549356284042</v>
+        <v>2.817615911188346</v>
       </c>
       <c r="C3" t="n">
-        <v>17.89235190989812</v>
+        <v>13.16032797542849</v>
       </c>
       <c r="D3" t="n">
-        <v>90.57604319381073</v>
+        <v>48.6946861306418</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.52690508420682</v>
+        <v>11.49921085984289</v>
       </c>
       <c r="C4" t="n">
-        <v>70.69270693970007</v>
+        <v>43.45706212848506</v>
       </c>
       <c r="D4" t="n">
-        <v>173.1007734650933</v>
+        <v>116.4725841364331</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.09181092477625</v>
+        <v>26.55627539987623</v>
       </c>
       <c r="C5" t="n">
-        <v>131.4069302134356</v>
+        <v>112.6064616771092</v>
       </c>
       <c r="D5" t="n">
-        <v>132.4868526881071</v>
+        <v>126.277298458746</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.74976181307086</v>
+        <v>32.76484788153306</v>
       </c>
       <c r="C6" t="n">
-        <v>156.1764247915826</v>
+        <v>225.6507828303124</v>
       </c>
       <c r="D6" t="n">
-        <v>61.50453017565419</v>
+        <v>80.30205346886787</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.15237618280328</v>
+        <v>20.00212772632452</v>
       </c>
       <c r="C7" t="n">
-        <v>141.8713789930023</v>
+        <v>260.6265265418093</v>
       </c>
       <c r="D7" t="n">
-        <v>36.23139902522853</v>
+        <v>48.50815406683489</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.60073178400781</v>
+        <v>7.34347282776614</v>
       </c>
       <c r="C8" t="n">
-        <v>102.0575825949772</v>
+        <v>167.3143524962627</v>
       </c>
       <c r="D8" t="n">
-        <v>30.70906818884022</v>
+        <v>42.47531442423825</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>58.68593251676156</v>
+        <v>78.65468082114168</v>
       </c>
       <c r="D9" t="n">
-        <v>29.39843500367073</v>
+        <v>42.93280885441725</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>37.72365553568369</v>
+        <v>44.12955930589413</v>
       </c>
       <c r="D10" t="n">
-        <v>30.60598467989432</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.8884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>33.58460721457913</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>26.25291535926396</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.51223562190536</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>19.97365704290136</v>
+        <v>17.51536079146734</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>42.98484148274235</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.164753687864217</v>
+        <v>0.3720823799095411</v>
       </c>
       <c r="C2" t="n">
-        <v>2.659554530804609</v>
+        <v>2.764601535159018</v>
       </c>
       <c r="D2" t="n">
-        <v>10.74817386609408</v>
+        <v>8.349764224619122</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.85660808191773</v>
+        <v>3.946625771072178</v>
       </c>
       <c r="C3" t="n">
-        <v>21.3628300444106</v>
+        <v>18.01016163440774</v>
       </c>
       <c r="D3" t="n">
-        <v>86.96321164218247</v>
+        <v>52.63640316319274</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.30467025014855</v>
+        <v>18.36555430334508</v>
       </c>
       <c r="C4" t="n">
-        <v>68.3316037109865</v>
+        <v>62.00129451400306</v>
       </c>
       <c r="D4" t="n">
-        <v>182.136779334981</v>
+        <v>122.4200117287603</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.88350048502668</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="C5" t="n">
-        <v>151.066427990978</v>
+        <v>179.4880240289231</v>
       </c>
       <c r="D5" t="n">
-        <v>143.6296891313084</v>
+        <v>117.5888312761617</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.87302005544945</v>
+        <v>12.39751000922872</v>
       </c>
       <c r="C6" t="n">
-        <v>190.3500806287099</v>
+        <v>231.3665179644373</v>
       </c>
       <c r="D6" t="n">
-        <v>59.93471559656354</v>
+        <v>68.06555008313562</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.324238784308704</v>
+        <v>4.850815406683489</v>
       </c>
       <c r="C7" t="n">
-        <v>143.9674103415693</v>
+        <v>117.6173019595849</v>
       </c>
       <c r="D7" t="n">
-        <v>36.23139902522853</v>
+        <v>36.9500383447372</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C8" t="n">
-        <v>76.18853058807372</v>
+        <v>57.91329707351935</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>31.62700229231099</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>28.73281006019139</v>
+        <v>33.61405964570653</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>27.06874770149305</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>25.90832191507333</v>
+        <v>25.76596849795754</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.96816746730337</v>
+        <v>22.0343454741154</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>14.30897278939726</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>36.19212911705866</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.667408512438584</v>
+        <v>0.2267837196810132</v>
       </c>
       <c r="C2" t="n">
-        <v>6.141813637768045</v>
+        <v>2.00374706436774</v>
       </c>
       <c r="D2" t="n">
-        <v>18.13386184514283</v>
+        <v>6.074073046175016</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.25221134900019</v>
+        <v>2.59181393921158</v>
       </c>
       <c r="C3" t="n">
-        <v>15.58033606639688</v>
+        <v>14.10280577150543</v>
       </c>
       <c r="D3" t="n">
-        <v>76.60086462385738</v>
+        <v>47.62948987153401</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.56519324467246</v>
+        <v>12.18839774822415</v>
       </c>
       <c r="C4" t="n">
-        <v>61.2993449054666</v>
+        <v>50.82115165804039</v>
       </c>
       <c r="D4" t="n">
-        <v>183.7704075148477</v>
+        <v>116.2556178937945</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.1119289049467</v>
+        <v>19.34042977366217</v>
       </c>
       <c r="C5" t="n">
-        <v>140.2917469368692</v>
+        <v>133.4195130071415</v>
       </c>
       <c r="D5" t="n">
-        <v>170.9959063871882</v>
+        <v>120.0922879219911</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.45291415348983</v>
+        <v>12.3572583533546</v>
       </c>
       <c r="C6" t="n">
-        <v>215.1853523030414</v>
+        <v>215.6683721735308</v>
       </c>
       <c r="D6" t="n">
-        <v>85.01149720613982</v>
+        <v>73.09700706740053</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.84620976779852</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>204.0336801305018</v>
+        <v>156.2441653831756</v>
       </c>
       <c r="D7" t="n">
-        <v>42.57937968088841</v>
+        <v>36.53083207502382</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>1.251728322914683</v>
       </c>
       <c r="C8" t="n">
-        <v>123.9211039685536</v>
+        <v>65.5905641207294</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>27.45457454926205</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>53.69374544066654</v>
+        <v>31.28437234352885</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>21.63281066307846</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>19.3600647277471</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>20.21418523044183</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>14.03801042302514</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.94732978133594</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>11.49921085984289</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.86995163914969</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.834886459237289</v>
+        <v>0.6067200812245288</v>
       </c>
       <c r="C2" t="n">
-        <v>3.390956570468483</v>
+        <v>5.577308707826131</v>
       </c>
       <c r="D2" t="n">
-        <v>14.43267300013236</v>
+        <v>7.270823497651877</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.14774518172253</v>
+        <v>1.575705065316131</v>
       </c>
       <c r="C3" t="n">
-        <v>19.67422399310608</v>
+        <v>10.30344215607028</v>
       </c>
       <c r="D3" t="n">
-        <v>74.12195167063418</v>
+        <v>41.43466185773664</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.08547847019426</v>
+        <v>8.308530821040756</v>
       </c>
       <c r="C4" t="n">
-        <v>53.00357680458105</v>
+        <v>41.60646770597982</v>
       </c>
       <c r="D4" t="n">
-        <v>182.0091521334289</v>
+        <v>114.1752945084956</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.38253141842033</v>
+        <v>19.38951715887451</v>
       </c>
       <c r="C5" t="n">
-        <v>134.352173326176</v>
+        <v>112.0419567471673</v>
       </c>
       <c r="D5" t="n">
-        <v>190.0908992347887</v>
+        <v>135.3093773378167</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.81896717845365</v>
+        <v>19.60255641069606</v>
       </c>
       <c r="C6" t="n">
-        <v>228.9111669561161</v>
+        <v>214.8633390560485</v>
       </c>
       <c r="D6" t="n">
-        <v>102.5209675113817</v>
+        <v>93.46434493970486</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.36711688812607</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>247.5113589607761</v>
+        <v>243.1995230437241</v>
       </c>
       <c r="D7" t="n">
-        <v>48.80758711663017</v>
+        <v>48.14883440708056</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.506221962492859</v>
+        <v>2.753802310412303</v>
       </c>
       <c r="C8" t="n">
-        <v>162.6412334240478</v>
+        <v>140.6942634956104</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>30.79251674370121</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.7765624340592268</v>
       </c>
       <c r="C9" t="n">
-        <v>65.45311944213483</v>
+        <v>57.243745139223</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>23.51874800293658</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>28.61303684027329</v>
       </c>
       <c r="D10" t="n">
-        <v>25.76596849795754</v>
+        <v>21.21065915025234</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.16670148773948</v>
+        <v>18.12502611580461</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.48041878474196</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>13.66887328622834</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>14.53673825678252</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.957024085191393</v>
+        <v>0.9866564427680444</v>
       </c>
       <c r="C2" t="n">
-        <v>9.12632665867835</v>
+        <v>6.600289815651307</v>
       </c>
       <c r="D2" t="n">
-        <v>17.11480772813465</v>
+        <v>9.778207134298231</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.771915737445251</v>
+        <v>1.840776945462769</v>
       </c>
       <c r="C3" t="n">
-        <v>16.4344565690916</v>
+        <v>16.84188186635403</v>
       </c>
       <c r="D3" t="n">
-        <v>69.71881321708723</v>
+        <v>37.74329048976863</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.90381408717959</v>
+        <v>5.564545987670921</v>
       </c>
       <c r="C4" t="n">
-        <v>51.07640606114455</v>
+        <v>32.77466535857552</v>
       </c>
       <c r="D4" t="n">
-        <v>176.2659280635851</v>
+        <v>109.5169016518444</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.93445355465628</v>
+        <v>16.19883712007237</v>
       </c>
       <c r="C5" t="n">
-        <v>117.8588118948296</v>
+        <v>93.09422605520381</v>
       </c>
       <c r="D5" t="n">
-        <v>207.3205714443202</v>
+        <v>145.740446695439</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.79508643838223</v>
+        <v>23.30570875111504</v>
       </c>
       <c r="C6" t="n">
-        <v>223.4369417572358</v>
+        <v>196.9916038479395</v>
       </c>
       <c r="D6" t="n">
-        <v>129.288318667671</v>
+        <v>112.2216165770444</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.56024344842221</v>
+        <v>16.34904451882213</v>
       </c>
       <c r="C7" t="n">
-        <v>286.317882214244</v>
+        <v>280.5687676581747</v>
       </c>
       <c r="D7" t="n">
-        <v>61.50354842794993</v>
+        <v>62.76116723709009</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.012443924985718</v>
+        <v>6.342090169434394</v>
       </c>
       <c r="C8" t="n">
-        <v>228.6490403190821</v>
+        <v>233.8228507204628</v>
       </c>
       <c r="D8" t="n">
-        <v>39.47116644924301</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>117.7046775052628</v>
+        <v>115.7078026748248</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>25.5156228333746</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>48.11545498513618</v>
+        <v>47.83074815090461</v>
       </c>
       <c r="D10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.20713307006285</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>25.23287949455151</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>19.36890045708532</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>15.4046032273367</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>9.316785713302231</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.713370728088937</v>
+        <v>5.865942532874692</v>
       </c>
       <c r="C2" t="n">
-        <v>3.051271864799086</v>
+        <v>7.87361658805942</v>
       </c>
       <c r="D2" t="n">
-        <v>7.071528713689775</v>
+        <v>11.87522023056942</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.092104357749953</v>
+        <v>0.8727737090754144</v>
       </c>
       <c r="C2" t="n">
-        <v>5.110978548308895</v>
+        <v>13.47350549308323</v>
       </c>
       <c r="D2" t="n">
-        <v>12.59680479319083</v>
+        <v>20.82974104100458</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.0656792851933</v>
+        <v>2.562361508084175</v>
       </c>
       <c r="C3" t="n">
-        <v>24.83330817892307</v>
+        <v>21.38246499849553</v>
       </c>
       <c r="D3" t="n">
-        <v>76.31124905110458</v>
+        <v>36.72227287735194</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.61999118966102</v>
+        <v>4.505240214788612</v>
       </c>
       <c r="C4" t="n">
-        <v>72.18594519785947</v>
+        <v>37.48410909584747</v>
       </c>
       <c r="D4" t="n">
-        <v>183.8980347163998</v>
+        <v>103.2759314959475</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.89483948912113</v>
+        <v>12.86089492563322</v>
       </c>
       <c r="C5" t="n">
-        <v>182.212373908208</v>
+        <v>76.99356370555611</v>
       </c>
       <c r="D5" t="n">
-        <v>189.8700060013331</v>
+        <v>151.8763698469816</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.56230475482195</v>
+        <v>22.90319219237384</v>
       </c>
       <c r="C6" t="n">
-        <v>236.7602398515693</v>
+        <v>173.1223719145868</v>
       </c>
       <c r="D6" t="n">
-        <v>98.17378867697681</v>
+        <v>130.1738550969016</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.928774385946488</v>
+        <v>21.79872602509618</v>
       </c>
       <c r="C7" t="n">
-        <v>160.7955477400638</v>
+        <v>286.0783357744078</v>
       </c>
       <c r="D7" t="n">
-        <v>36.17151241526948</v>
+        <v>76.77463396750906</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>11.34900346109313</v>
       </c>
       <c r="C8" t="n">
-        <v>86.70304850055705</v>
+        <v>301.4161801578557</v>
       </c>
       <c r="D8" t="n">
-        <v>24.95111790343269</v>
+        <v>43.22635141798705</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>3.660937189136355</v>
       </c>
       <c r="C9" t="n">
-        <v>36.72030938194344</v>
+        <v>194.806233458286</v>
       </c>
       <c r="D9" t="n">
-        <v>20.85624822901923</v>
+        <v>28.06718511671205</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>22.49183990429443</v>
+        <v>88.11676519467248</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>23.34596040698915</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.8811517745239</v>
+        <v>38.38240824523329</v>
       </c>
       <c r="D11" t="n">
-        <v>16.52575910558656</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.28224461720434</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>16.05550195525234</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>10.40652566501619</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.7166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.850234569606743</v>
+        <v>4.033019569045897</v>
       </c>
       <c r="C2" t="n">
-        <v>4.468915549731481</v>
+        <v>5.236642254452487</v>
       </c>
       <c r="D2" t="n">
-        <v>20.62848276163398</v>
+        <v>18.85348291235575</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.0187353218387</v>
+        <v>9.684941102394784</v>
       </c>
       <c r="C3" t="n">
-        <v>7.809802987283376</v>
+        <v>15.54597489674824</v>
       </c>
       <c r="D3" t="n">
-        <v>9.360964359993337</v>
+        <v>11.11829275059513</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39945745800067</v>
+        <v>11.67779938034382</v>
       </c>
       <c r="C21" t="n">
-        <v>70.1501008095329</v>
+        <v>59.94603681909829</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576406759764784</v>
+        <v>0.7785199586895881</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.158683275189489</v>
+        <v>2.488730430265664</v>
       </c>
       <c r="C2" t="n">
-        <v>5.867906028283186</v>
+        <v>3.567671157232909</v>
       </c>
       <c r="D2" t="n">
-        <v>27.04125876577415</v>
+        <v>17.94045754740621</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.11538856521139</v>
+        <v>12.50255701358313</v>
       </c>
       <c r="C3" t="n">
-        <v>13.93099992326224</v>
+        <v>18.83482970597506</v>
       </c>
       <c r="D3" t="n">
-        <v>24.42588288166064</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.74170254279185</v>
+        <v>11.9586687854304</v>
       </c>
       <c r="C4" t="n">
-        <v>12.63509295365645</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D4" t="n">
-        <v>19.97365704290135</v>
+        <v>20.10128424445344</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.50089661781091</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>5.433973543006096</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.58292145661112</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44485546761624</v>
+        <v>13.62892704366261</v>
       </c>
       <c r="C21" t="n">
-        <v>86.16603576670116</v>
+        <v>73.75654635393883</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251548519498157</v>
+        <v>1.603403181607366</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.264712027248144</v>
+        <v>2.02829075697391</v>
       </c>
       <c r="C2" t="n">
-        <v>8.552985999398212</v>
+        <v>8.607963870836034</v>
       </c>
       <c r="D2" t="n">
-        <v>32.3633130704961</v>
+        <v>24.67819204165207</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.15327581504952</v>
+        <v>10.28871594050657</v>
       </c>
       <c r="C3" t="n">
-        <v>19.3306122966197</v>
+        <v>15.67851083682156</v>
       </c>
       <c r="D3" t="n">
-        <v>40.38910055271378</v>
+        <v>33.95865308989718</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.69211643596077</v>
+        <v>19.48867367700343</v>
       </c>
       <c r="C4" t="n">
-        <v>25.72964383290041</v>
+        <v>39.28365263773187</v>
       </c>
       <c r="D4" t="n">
-        <v>27.72062817711294</v>
+        <v>28.48639138642545</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.75013736150258</v>
+        <v>10.94648690235194</v>
       </c>
       <c r="C5" t="n">
-        <v>15.56070111231195</v>
+        <v>31.04777114680538</v>
       </c>
       <c r="D5" t="n">
-        <v>29.62423697564751</v>
+        <v>26.99806186678729</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>20.00212772632452</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>24.03318379996192</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>24.18437294641592</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>42.09145107187774</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74244024856455</v>
+        <v>14.84143113916844</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1288855162437</v>
+        <v>87.39953893065858</v>
       </c>
       <c r="D21" t="n">
-        <v>5.022732074569364</v>
+        <v>2.473571856528073</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.58279828342411</v>
+        <v>1.715113239319178</v>
       </c>
       <c r="C2" t="n">
-        <v>5.849252821902496</v>
+        <v>5.298492359820036</v>
       </c>
       <c r="D2" t="n">
-        <v>33.78390199854124</v>
+        <v>20.12484618935536</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.85875150377547</v>
+        <v>8.438121518001337</v>
       </c>
       <c r="C3" t="n">
-        <v>27.47911824186822</v>
+        <v>26.67899386290707</v>
       </c>
       <c r="D3" t="n">
-        <v>55.99888905023806</v>
+        <v>45.81816535719864</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.21462719879833</v>
+        <v>20.02470792352219</v>
       </c>
       <c r="C4" t="n">
-        <v>38.60722846950582</v>
+        <v>39.30917807804229</v>
       </c>
       <c r="D4" t="n">
-        <v>40.70031457496002</v>
+        <v>38.82419471214436</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.65382827549515</v>
+        <v>20.78850763742621</v>
       </c>
       <c r="C5" t="n">
-        <v>33.13398501832986</v>
+        <v>55.17422097867075</v>
       </c>
       <c r="D5" t="n">
-        <v>33.03581024790518</v>
+        <v>31.48955761371645</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.22392059202629</v>
+        <v>9.861655689159212</v>
       </c>
       <c r="C6" t="n">
-        <v>18.8377749490878</v>
+        <v>32.04031807579891</v>
       </c>
       <c r="D6" t="n">
-        <v>38.15856976866503</v>
+        <v>33.89189424600839</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>17.6066633279623</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>25.95250056176443</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>27.95624762613216</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>27.61656292046278</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>43.39324852770902</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07349467301713</v>
+        <v>16.08734664961764</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9080366763498</v>
+        <v>101.604294629164</v>
       </c>
       <c r="D21" t="n">
-        <v>6.885140827816048</v>
+        <v>3.386809820972134</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.692173189223006</v>
+        <v>2.448478774391545</v>
       </c>
       <c r="C2" t="n">
-        <v>8.016951752879454</v>
+        <v>6.764241682260523</v>
       </c>
       <c r="D2" t="n">
-        <v>32.63427543686822</v>
+        <v>27.87574431438393</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.71992416684918</v>
+        <v>7.102944640225672</v>
       </c>
       <c r="C3" t="n">
-        <v>23.24778563656447</v>
+        <v>23.09070600388498</v>
       </c>
       <c r="D3" t="n">
-        <v>65.11932522269093</v>
+        <v>50.91834468076082</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.25443688631594</v>
+        <v>17.99543541884404</v>
       </c>
       <c r="C4" t="n">
-        <v>46.77536936883928</v>
+        <v>54.93074754801754</v>
       </c>
       <c r="D4" t="n">
-        <v>50.82115165804039</v>
+        <v>51.90598287123311</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.04590546238812</v>
+        <v>25.84450831429729</v>
       </c>
       <c r="C5" t="n">
-        <v>40.15348110369455</v>
+        <v>64.79534848028949</v>
       </c>
       <c r="D5" t="n">
-        <v>32.64311116620645</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.3107153006275</v>
+        <v>19.0390332284584</v>
       </c>
       <c r="C6" t="n">
-        <v>24.59376173908685</v>
+        <v>61.42402686390595</v>
       </c>
       <c r="D6" t="n">
-        <v>30.83276839957533</v>
+        <v>36.46800022195202</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.210135066437822</v>
+        <v>9.282424543653592</v>
       </c>
       <c r="C7" t="n">
-        <v>15.69029180927252</v>
+        <v>32.39865598784899</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>36.71049190490098</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.20146356801562</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>22.18749811597791</v>
+        <v>30.95155987178918</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.2734342500619</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>42.40659208494097</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.065948959722752</v>
+        <v>17.3624494763637</v>
       </c>
       <c r="C21" t="n">
-        <v>66.2432714974008</v>
+        <v>115.4602890178186</v>
       </c>
       <c r="D21" t="n">
-        <v>5.299461719792064</v>
+        <v>4.340612369090926</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.73398742987812</v>
+        <v>3.298672286269283</v>
       </c>
       <c r="C2" t="n">
-        <v>5.647012794827654</v>
+        <v>9.161669576031233</v>
       </c>
       <c r="D2" t="n">
-        <v>37.21118323406685</v>
+        <v>26.95584671550467</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.5585576904542</v>
+        <v>7.731263170943632</v>
       </c>
       <c r="C3" t="n">
-        <v>28.55413197801848</v>
+        <v>24.80385574779567</v>
       </c>
       <c r="D3" t="n">
-        <v>77.47462008063705</v>
+        <v>60.15168183920207</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.38955821660351</v>
+        <v>15.81301027230337</v>
       </c>
       <c r="C4" t="n">
-        <v>54.19050977901544</v>
+        <v>56.42398580617694</v>
       </c>
       <c r="D4" t="n">
-        <v>74.29179402346888</v>
+        <v>63.72426173495622</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.04085785514665</v>
+        <v>26.50718801466389</v>
       </c>
       <c r="C5" t="n">
-        <v>68.94323253073227</v>
+        <v>83.81671025007145</v>
       </c>
       <c r="D5" t="n">
-        <v>44.76769531365456</v>
+        <v>47.81111319681967</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.84406634594078</v>
+        <v>26.96860943565989</v>
       </c>
       <c r="C6" t="n">
-        <v>48.02022545782425</v>
+        <v>81.67060976858792</v>
       </c>
       <c r="D6" t="n">
-        <v>34.41516577237194</v>
+        <v>40.29190752999335</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.00106386316226</v>
+        <v>15.69029180927252</v>
       </c>
       <c r="C7" t="n">
-        <v>27.5478405811655</v>
+        <v>60.66513588852315</v>
       </c>
       <c r="D7" t="n">
-        <v>33.65627479698915</v>
+        <v>38.68675003354981</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>9.179341034707678</v>
       </c>
       <c r="C8" t="n">
-        <v>20.27799883121787</v>
+        <v>34.29735604786232</v>
       </c>
       <c r="D8" t="n">
-        <v>32.46148784092078</v>
+        <v>39.13737222979909</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>32.06093477758807</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>39.160934174701</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>34.44952694202058</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>34.11769621798515</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>47.26722496866692</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>44.69504598354028</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>43.1870815098172</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>31.03599017435442</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.290486438529825</v>
+        <v>18.65919322636027</v>
       </c>
       <c r="C21" t="n">
-        <v>75.63879679974694</v>
+        <v>128.8372865629637</v>
       </c>
       <c r="D21" t="n">
-        <v>6.379175633713597</v>
+        <v>5.331198064674362</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.061490252469055</v>
+        <v>2.875539025738908</v>
       </c>
       <c r="C2" t="n">
-        <v>2.839214360681776</v>
+        <v>5.569454726192155</v>
       </c>
       <c r="D2" t="n">
-        <v>33.5816619714664</v>
+        <v>21.03296281578367</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.0971362694582</v>
+        <v>10.57833151325938</v>
       </c>
       <c r="C3" t="n">
-        <v>24.5633275602552</v>
+        <v>39.68715094417731</v>
       </c>
       <c r="D3" t="n">
-        <v>89.26541000864124</v>
+        <v>67.22517404830033</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.85200244303276</v>
+        <v>12.72443199474291</v>
       </c>
       <c r="C4" t="n">
-        <v>63.89017709697393</v>
+        <v>77.58457582351268</v>
       </c>
       <c r="D4" t="n">
-        <v>96.43511349275569</v>
+        <v>59.89544568839366</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.15223731408305</v>
+        <v>15.19254572321939</v>
       </c>
       <c r="C5" t="n">
-        <v>87.13010875190443</v>
+        <v>48.79286090106649</v>
       </c>
       <c r="D5" t="n">
-        <v>60.86835766330226</v>
+        <v>38.28816046562561</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.21641076775758</v>
+        <v>9.740900721536855</v>
       </c>
       <c r="C6" t="n">
-        <v>82.39513957432206</v>
+        <v>39.92964262712628</v>
       </c>
       <c r="D6" t="n">
-        <v>41.0164373357275</v>
+        <v>25.47929816831747</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.48689010804419</v>
+        <v>6.048547605864599</v>
       </c>
       <c r="C7" t="n">
-        <v>50.72395863531995</v>
+        <v>24.07441720354028</v>
       </c>
       <c r="D7" t="n">
-        <v>36.05173919535137</v>
+        <v>27.48795397120644</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.511752595819845</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>29.29044275620359</v>
+        <v>23.61594102565702</v>
       </c>
       <c r="D8" t="n">
-        <v>34.63115026730623</v>
+        <v>28.78975142703771</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>25.07187287105504</v>
+        <v>26.29218526743382</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>37.01188845010476</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>24.58296251434014</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.502138949161433</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>85.33683054671131</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.502138949161433</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
